--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z918"/>
+  <dimension ref="A1:Z921"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45187</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44208</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44742</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>44760</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44923</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44965</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44977</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44977</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45070</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45077</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43318</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>43322</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>43340</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>43340</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>43340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>43355</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>43355</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>43362</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>43368</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43376</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43377</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43383</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>43383</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>43384</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>43385</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>43391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>43402</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>43411</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>43411</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>43412</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>43416</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>43418</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>43418</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>43418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>43419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>43419</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>43419</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>43420</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>43423</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>43423</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43429</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43430</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43430</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43431</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43437</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43438</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43440</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43440</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43446</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43446</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43461</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43461</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43467</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43487</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43490</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43493</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43493</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43493</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>43494</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>43495</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>43495</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>43495</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>43495</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>43499</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43501</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>43503</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>43503</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43503</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>43504</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>43504</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>43504</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>43504</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>43509</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>43509</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>43510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>43516</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>43516</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>43516</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>43517</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>43524</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>43529</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>43529</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>43529</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>43530</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>43530</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>43535</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>43539</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>43541</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>43543</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>43543</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>43545</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>43551</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>43556</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43557</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43557</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43558</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43558</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43563</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>43566</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>43567</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>43567</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>43579</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>43579</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>43584</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43587</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43587</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>43599</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>43600</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43602</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43605</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43605</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>43607</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>43612</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43612</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>43619</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>43623</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>43634</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>43643</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>43648</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43650</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43650</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43650</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43650</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43650</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43654</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43656</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43657</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43663</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43664</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43678</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43689</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43690</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43691</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>43691</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43692</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>43692</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>43696</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>43697</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>43697</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>43704</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>43704</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>43710</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>43713</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>43713</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>43717</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>43720</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>43725</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43727</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>43727</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>43727</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>43742</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>43760</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43771</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43771</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43775</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43782</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43787</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43791</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>43791</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>43791</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>43791</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>43797</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>43797</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>43804</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>43805</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>43810</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>43810</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>43810</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>43810</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>43811</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>43815</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>43838</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>43838</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>43838</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>43838</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43841</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>43847</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>43858</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>43865</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>43868</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>43871</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>43882</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>43885</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>43886</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>43886</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>43889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>43889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43893</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>43893</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>43899</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>43901</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>43902</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>43902</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43903</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43908</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>43909</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>43909</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>43910</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>43922</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>43923</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>43937</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>43937</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43937</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43937</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43943</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43943</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43948</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43949</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43955</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43966</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43969</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43974</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43975</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43989</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43998</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44000</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44004</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44004</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44004</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44014</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44015</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44022</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44022</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44022</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44022</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44022</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44022</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44025</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44027</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44039</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44047</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44055</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44064</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44064</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44066</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44066</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44066</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44069</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44070</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44078</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44081</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44083</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44083</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44083</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44088</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44090</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>44099</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44100</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44103</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>44111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44118</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44119</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44126</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44133</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44133</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44138</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44138</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44145</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44146</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44159</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>44159</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44161</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44161</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44165</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>44165</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44166</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>44173</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44209</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44215</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44216</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44224</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44228</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44228</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44232</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44235</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>44236</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>44236</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44237</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44237</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44239</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44242</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44243</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44243</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44245</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>44250</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44250</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44250</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44265</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44266</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44271</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44272</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44273</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44273</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44273</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44273</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44275</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44278</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44284</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44284</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44285</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44287</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44293</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44297</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44299</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44302</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44302</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44305</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44308</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44316</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44319</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44322</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44323</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44328</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44333</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44337</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44340</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44343</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44344</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44353</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44353</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44353</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44353</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44354</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44355</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44356</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44358</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44358</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44358</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>44358</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44358</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44358</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44362</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44365</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44365</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44365</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44376</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44378</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44378</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44378</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>44378</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44378</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44379</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44386</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44386</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44389</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44389</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44392</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44396</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44397</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44400</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44406</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44406</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44414</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44414</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44414</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44414</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44417</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44425</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44428</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44432</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44432</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44433</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44435</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44441</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44447</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44449</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44454</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44455</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44455</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44455</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44455</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44456</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>44456</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>44456</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44459</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44462</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>44463</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44465</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>44467</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44467</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44469</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44469</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44473</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44473</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44474</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44488</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44488</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44489</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44489</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44489</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44495</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44495</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44496</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44496</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44497</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44498</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44502</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44507</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44508</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44516</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44522</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44523</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44523</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44523</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44529</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44530</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44544</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44544</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44547</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44550</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44551</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44551</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44551</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44551</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44551</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44553</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44558</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44558</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44558</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44563</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44563</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44571</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44575</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44575</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44578</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44578</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44585</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>44594</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44594</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44606</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44606</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44606</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44606</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44607</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44607</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44614</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44614</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44615</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44621</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44626</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44638</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44648</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44651</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44657</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44662</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44662</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44694</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44694</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44697</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44699</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44700</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44712</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44712</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44712</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>44712</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>44715</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44721</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>44729</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>44732</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44735</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44735</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>44735</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44739</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44739</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44739</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>44739</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>44748</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>44748</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44748</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44748</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44749</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>44749</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44753</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>44753</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44767</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>44771</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>44776</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>44776</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>44791</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44802</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>44802</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44802</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44802</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44802</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44802</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44806</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44806</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44809</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44809</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44810</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44810</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44812</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44812</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44817</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44817</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44818</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44819</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44820</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44824</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44824</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44840</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44840</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44840</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44840</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44840</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>44840</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>44845</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44853</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44853</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>44855</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44860</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44860</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44865</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44866</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44866</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44867</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44867</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44873</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>44873</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>44880</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>44887</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>44888</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44893</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44893</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44894</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44894</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44896</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44896</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44896</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44896</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>44902</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44903</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44903</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44903</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44907</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44908</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>44909</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44910</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44910</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44915</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44923</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44923</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>44923</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>44926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>44931</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>44931</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44931</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>44931</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44931</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44931</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44935</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44938</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44943</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44945</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44949</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44949</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>44950</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44951</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>44952</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44952</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>44958</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>44958</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>44961</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>44966</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>44966</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>44970</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44970</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44971</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>44971</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>44971</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>44972</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>44972</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>44974</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>44974</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44974</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>44974</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>44977</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>44986</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>44986</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44986</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>44986</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>44995</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45000</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>45002</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45008</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45008</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45008</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>45009</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45009</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45009</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45009</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>45012</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45012</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45012</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45012</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45026</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45027</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45027</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45042</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45042</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45042</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45051</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45051</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45054</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45054</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45062</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45075</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45077</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45078</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45084</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45089</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45089</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45089</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45091</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45091</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45092</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45093</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45093</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45093</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45093</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45095</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45096</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45096</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45096</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45097</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45097</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45097</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45097</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45097</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45097</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45098</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>45098</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>45098</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45099</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45100</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45100</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45100</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45100</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45103</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45103</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45103</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45104</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45104</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45105</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45110</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45110</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45110</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45110</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45112</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45112</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45113</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45113</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45113</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45117</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45118</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45118</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45119</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45120</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45125</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45131</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45133</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45135</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45140</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45153</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45154</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45154</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45155</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45155</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45159</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45159</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45159</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45161</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45161</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45163</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45163</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45163</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45163</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45166</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45167</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45167</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45169</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45170</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45174</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45174</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45175</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45175</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45176</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45176</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>45177</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45177</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45180</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45182</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45183</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45187</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45187</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45189</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45189</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>45189</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45190</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45190</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45190</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45191</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45191</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45191</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45191</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>45191</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45191</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45196</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45198</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45198</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45198</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45199</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45201</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45201</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45204</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45204</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45211</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45211</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45211</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45211</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45211</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45211</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45212</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45212</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45212</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45218</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45223</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45229</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45230</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45231</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45231</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45233</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45235</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45235</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45235</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45235</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45235</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45235</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45236</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45237</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45237</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45240</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45244</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45245</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45246</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45247</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45247</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45250</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45250</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45250</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45250</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45250</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45251</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45254</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45257</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45258</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45259</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45260</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45266</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45266</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
         <v>45270</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45271</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45273</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50828,7 +50828,7 @@
         <v>45273</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45273</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45273</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50999,7 +50999,7 @@
         <v>45273</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45274</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>45274</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45282</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45282</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45282</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45301</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>45305</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45308</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45308</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45308</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51619,14 +51619,14 @@
     <row r="885" ht="15" customHeight="1">
       <c r="A885" t="inlineStr">
         <is>
-          <t>A 2879-2024</t>
+          <t>A 2880-2024</t>
         </is>
       </c>
       <c r="B885" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -51676,14 +51676,14 @@
     <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
-          <t>A 2880-2024</t>
+          <t>A 2879-2024</t>
         </is>
       </c>
       <c r="B886" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H886" t="n">
         <v>0</v>
@@ -51733,14 +51733,14 @@
     <row r="887" ht="15" customHeight="1">
       <c r="A887" t="inlineStr">
         <is>
-          <t>A 3161-2024</t>
+          <t>A 3158-2024</t>
         </is>
       </c>
       <c r="B887" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>45316</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -51847,14 +51847,14 @@
     <row r="889" ht="15" customHeight="1">
       <c r="A889" t="inlineStr">
         <is>
-          <t>A 3158-2024</t>
+          <t>A 3159-2024</t>
         </is>
       </c>
       <c r="B889" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         </is>
       </c>
       <c r="G889" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H889" t="n">
         <v>0</v>
@@ -51904,14 +51904,14 @@
     <row r="890" ht="15" customHeight="1">
       <c r="A890" t="inlineStr">
         <is>
-          <t>A 3159-2024</t>
+          <t>A 3161-2024</t>
         </is>
       </c>
       <c r="B890" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         </is>
       </c>
       <c r="G890" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -51968,7 +51968,7 @@
         <v>45317</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52018,14 +52018,14 @@
     <row r="892" ht="15" customHeight="1">
       <c r="A892" t="inlineStr">
         <is>
-          <t>A 3554-2024</t>
+          <t>A 3455-2024</t>
         </is>
       </c>
       <c r="B892" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         </is>
       </c>
       <c r="G892" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -52075,14 +52075,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 3579-2024</t>
+          <t>A 3439-2024</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -52132,14 +52132,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 3583-2024</t>
+          <t>A 3552-2024</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         </is>
       </c>
       <c r="G894" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -52189,14 +52189,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 3455-2024</t>
+          <t>A 3556-2024</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52246,14 +52246,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 3582-2024</t>
+          <t>A 3584-2024</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -52303,14 +52303,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 3553-2024</t>
+          <t>A 3554-2024</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -52360,14 +52360,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 3581-2024</t>
+          <t>A 3553-2024</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>8.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -52417,14 +52417,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 3439-2024</t>
+          <t>A 3582-2024</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -52474,14 +52474,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 3552-2024</t>
+          <t>A 3585-2024</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -52531,14 +52531,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 3556-2024</t>
+          <t>A 3581-2024</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -52588,14 +52588,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 3584-2024</t>
+          <t>A 3583-2024</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -52645,14 +52645,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 3585-2024</t>
+          <t>A 3579-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -52702,14 +52702,14 @@
     <row r="904" ht="15" customHeight="1">
       <c r="A904" t="inlineStr">
         <is>
-          <t>A 3975-2024</t>
+          <t>A 3899-2024</t>
         </is>
       </c>
       <c r="B904" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         </is>
       </c>
       <c r="G904" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -52759,14 +52759,14 @@
     <row r="905" ht="15" customHeight="1">
       <c r="A905" t="inlineStr">
         <is>
-          <t>A 3899-2024</t>
+          <t>A 3975-2024</t>
         </is>
       </c>
       <c r="B905" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         </is>
       </c>
       <c r="G905" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -52823,7 +52823,7 @@
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -52885,7 +52885,7 @@
         <v>45324</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -52947,7 +52947,7 @@
         <v>45328</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45328</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53054,14 +53054,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 4990-2024</t>
+          <t>A 4992-2024</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53111,14 +53111,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 4994-2024</t>
+          <t>A 4991-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53168,14 +53168,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 4991-2024</t>
+          <t>A 4990-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53225,14 +53225,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 4992-2024</t>
+          <t>A 4994-2024</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         </is>
       </c>
       <c r="G913" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -53289,7 +53289,7 @@
         <v>45331</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45331</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53403,7 +53403,7 @@
         <v>45331</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53460,7 +53460,7 @@
         <v>45331</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="R917" s="2" t="inlineStr"/>
     </row>
-    <row r="918">
+    <row r="918" ht="15" customHeight="1">
       <c r="A918" t="inlineStr">
         <is>
           <t>A 5335-2024</t>
@@ -53517,7 +53517,7 @@
         <v>45331</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53563,6 +53563,177 @@
         <v>0</v>
       </c>
       <c r="R918" s="2" t="inlineStr"/>
+    </row>
+    <row r="919" ht="15" customHeight="1">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>A 6202-2024</t>
+        </is>
+      </c>
+      <c r="B919" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C919" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>GISLAVED</t>
+        </is>
+      </c>
+      <c r="G919" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H919" t="n">
+        <v>0</v>
+      </c>
+      <c r="I919" t="n">
+        <v>0</v>
+      </c>
+      <c r="J919" t="n">
+        <v>0</v>
+      </c>
+      <c r="K919" t="n">
+        <v>0</v>
+      </c>
+      <c r="L919" t="n">
+        <v>0</v>
+      </c>
+      <c r="M919" t="n">
+        <v>0</v>
+      </c>
+      <c r="N919" t="n">
+        <v>0</v>
+      </c>
+      <c r="O919" t="n">
+        <v>0</v>
+      </c>
+      <c r="P919" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q919" t="n">
+        <v>0</v>
+      </c>
+      <c r="R919" s="2" t="inlineStr"/>
+    </row>
+    <row r="920" ht="15" customHeight="1">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>A 6201-2024</t>
+        </is>
+      </c>
+      <c r="B920" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C920" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>GISLAVED</t>
+        </is>
+      </c>
+      <c r="G920" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H920" t="n">
+        <v>0</v>
+      </c>
+      <c r="I920" t="n">
+        <v>0</v>
+      </c>
+      <c r="J920" t="n">
+        <v>0</v>
+      </c>
+      <c r="K920" t="n">
+        <v>0</v>
+      </c>
+      <c r="L920" t="n">
+        <v>0</v>
+      </c>
+      <c r="M920" t="n">
+        <v>0</v>
+      </c>
+      <c r="N920" t="n">
+        <v>0</v>
+      </c>
+      <c r="O920" t="n">
+        <v>0</v>
+      </c>
+      <c r="P920" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q920" t="n">
+        <v>0</v>
+      </c>
+      <c r="R920" s="2" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>A 6207-2024</t>
+        </is>
+      </c>
+      <c r="B921" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C921" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>GISLAVED</t>
+        </is>
+      </c>
+      <c r="G921" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H921" t="n">
+        <v>0</v>
+      </c>
+      <c r="I921" t="n">
+        <v>0</v>
+      </c>
+      <c r="J921" t="n">
+        <v>0</v>
+      </c>
+      <c r="K921" t="n">
+        <v>0</v>
+      </c>
+      <c r="L921" t="n">
+        <v>0</v>
+      </c>
+      <c r="M921" t="n">
+        <v>0</v>
+      </c>
+      <c r="N921" t="n">
+        <v>0</v>
+      </c>
+      <c r="O921" t="n">
+        <v>0</v>
+      </c>
+      <c r="P921" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q921" t="n">
+        <v>0</v>
+      </c>
+      <c r="R921" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -569,7 +569,7 @@
         <v>45187</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44208</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44742</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>44760</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44923</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44965</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44977</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44977</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45070</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45077</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43318</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>43322</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>43340</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>43340</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>43340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>43355</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>43355</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>43362</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>43368</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43376</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43377</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43383</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>43383</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>43384</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>43385</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>43391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>43402</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>43411</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>43411</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>43412</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>43416</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>43418</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>43418</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>43418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>43419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>43419</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>43419</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>43420</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>43423</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>43423</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43429</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43430</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43430</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43431</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43437</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43438</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43440</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43440</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43446</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43446</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43461</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43461</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43467</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43487</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43490</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43493</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43493</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43493</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>43494</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>43495</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>43495</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>43495</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>43495</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>43499</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43501</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>43503</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>43503</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43503</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>43504</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>43504</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>43504</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>43504</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>43509</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>43509</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>43510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>43516</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>43516</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>43516</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>43517</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>43524</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>43529</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>43529</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>43529</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>43530</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>43530</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>43535</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>43539</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>43541</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>43543</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>43543</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>43545</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>43551</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>43556</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43557</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43557</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43558</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43558</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43563</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>43566</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>43567</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>43567</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>43579</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>43579</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>43584</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43587</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43587</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>43599</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>43600</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43602</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43605</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43605</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>43607</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>43612</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43612</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>43619</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>43623</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>43634</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>43643</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>43648</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43650</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43650</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43650</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43650</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43650</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43654</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43656</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43657</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43663</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43664</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43678</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43689</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43690</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43691</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>43691</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43692</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>43692</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>43696</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>43697</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>43697</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>43704</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>43704</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>43710</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>43713</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>43713</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>43717</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>43720</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>43725</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43727</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>43727</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>43727</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>43742</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>43760</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43771</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43771</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43775</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43782</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43787</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43791</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>43791</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>43791</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>43791</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>43797</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>43797</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>43804</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>43805</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>43810</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>43810</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>43810</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>43810</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>43811</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>43815</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>43838</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>43838</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>43838</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>43838</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43841</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>43847</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>43858</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>43865</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>43868</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>43871</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>43882</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>43885</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>43886</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>43886</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>43889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>43889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43893</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>43893</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>43899</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>43901</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>43902</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>43902</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43903</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43908</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>43909</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>43909</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>43910</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>43922</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>43923</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>43937</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>43937</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43937</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43937</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43943</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43943</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43948</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43949</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43955</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43966</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43969</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43974</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43975</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43989</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43998</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44000</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44004</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44004</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44004</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44014</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44015</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44022</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44022</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44022</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44022</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44022</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44022</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44025</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44027</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44039</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44047</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44055</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44064</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44064</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44066</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44066</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44066</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44069</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44070</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44078</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44081</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44083</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44083</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44083</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44088</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44090</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>44099</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44100</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44103</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>44111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44118</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44119</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44126</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44133</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44133</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44138</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44138</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44145</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44146</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44159</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>44159</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44161</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44161</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44165</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>44165</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44166</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>44173</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44209</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44215</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44216</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44224</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44228</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44228</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44232</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44235</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>44236</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>44236</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44237</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44237</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44239</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44242</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44243</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44243</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44245</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>44250</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44250</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44250</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44265</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44266</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44271</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44272</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44273</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44273</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44273</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44273</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44275</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44278</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44284</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44284</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44285</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44287</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44293</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44297</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44299</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44302</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44302</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44305</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44308</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44316</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44319</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44322</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44323</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44328</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44333</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44337</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44340</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44343</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44344</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44353</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44353</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44353</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44353</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44354</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44355</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44356</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44358</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44358</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44358</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>44358</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44358</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44358</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44362</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44365</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44365</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44365</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44376</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44378</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44378</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44378</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>44378</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44378</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44379</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44386</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44386</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44389</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44389</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44392</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44396</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44397</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44400</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44406</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44406</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44414</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44414</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44414</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44414</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44417</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44425</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44428</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44432</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44432</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44433</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44435</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44441</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44447</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44449</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44454</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44455</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44455</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44455</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44455</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44456</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>44456</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>44456</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44459</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44462</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>44463</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44465</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>44467</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44467</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44469</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44469</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44473</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44473</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44474</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44488</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44488</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44489</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44489</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44489</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44495</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44495</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44496</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44496</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44497</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44498</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44502</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44507</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44508</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44516</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44522</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44523</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44523</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44523</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44529</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44530</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44544</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44544</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44547</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44550</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44551</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44551</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44551</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44551</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44551</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44553</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44558</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44558</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44558</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44563</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44563</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44571</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44575</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44575</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44578</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44578</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44585</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>44594</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44594</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44606</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44606</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44606</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44606</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44607</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44607</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44614</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44614</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44615</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44621</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44626</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44638</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44648</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44651</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44657</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44662</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44662</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44694</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44694</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44697</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44699</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44700</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44712</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44712</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44712</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>44712</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>44715</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44721</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>44729</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>44732</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44735</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44735</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>44735</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44739</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44739</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44739</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>44739</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>44748</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>44748</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44748</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44748</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44749</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>44749</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44753</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>44753</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44767</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>44771</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>44776</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>44776</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>44791</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44802</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>44802</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44802</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44802</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44802</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44802</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44806</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44806</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44809</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44809</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44810</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44810</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44812</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44812</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44817</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44817</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44818</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44819</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44820</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44824</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44824</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44840</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44840</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44840</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44840</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44840</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>44840</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>44845</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44853</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44853</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>44855</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44860</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44860</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44865</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44866</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44866</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44867</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44867</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44873</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>44873</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>44880</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>44887</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>44888</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44893</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44893</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44894</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44894</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44896</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44896</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44896</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44896</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>44902</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44903</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44903</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44903</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44907</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44908</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>44909</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44910</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44910</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44915</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44923</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44923</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>44923</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>44926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>44931</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>44931</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44931</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>44931</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44931</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44931</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44935</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44938</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44943</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44945</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44949</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44949</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>44950</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44951</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>44952</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44952</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>44958</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>44958</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>44961</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>44966</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>44966</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>44970</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44970</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44971</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>44971</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>44971</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>44972</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>44972</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>44974</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>44974</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44974</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>44974</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>44977</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>44986</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>44986</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44986</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>44986</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>44995</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45000</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>45002</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45008</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45008</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45008</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>45009</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45009</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45009</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45009</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>45012</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45012</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45012</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45012</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45026</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45027</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45027</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45042</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45042</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45042</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45051</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45051</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45054</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45054</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45062</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45075</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45077</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45078</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45084</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45089</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45089</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45089</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45091</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45091</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45092</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45093</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45093</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45093</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45093</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45095</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45096</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45096</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45096</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45097</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45097</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45097</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45097</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45097</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45097</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45098</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>45098</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>45098</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45099</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45100</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45100</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45100</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45100</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45103</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45103</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45103</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45104</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45104</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45105</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45110</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45110</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45110</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45110</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45112</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45112</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45113</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45113</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45113</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45117</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45118</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45118</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45119</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45120</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45125</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45131</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45133</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45135</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45140</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45153</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45154</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45154</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45155</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45155</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45159</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45159</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45159</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45161</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45161</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45163</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45163</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45163</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45163</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45166</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45167</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45167</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45169</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45170</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45174</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45174</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45175</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45175</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45176</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45176</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>45177</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45177</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45180</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45182</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45183</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45187</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45187</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45189</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45189</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>45189</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45190</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45190</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45190</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45191</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45191</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45191</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45191</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>45191</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45191</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45196</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45198</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45198</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45198</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45199</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45201</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45201</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45204</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45204</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45211</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45211</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45211</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45211</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45211</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45211</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45212</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45212</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45212</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45218</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45223</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45229</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45230</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45231</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45231</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45233</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45235</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45235</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45235</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45235</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45235</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45235</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45236</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45237</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45237</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45240</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45244</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45245</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45246</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45247</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45247</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45250</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45250</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45250</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45250</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45250</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45251</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45254</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45257</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45258</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45259</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45260</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45266</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45266</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
         <v>45270</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45271</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45273</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50828,7 +50828,7 @@
         <v>45273</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45273</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45273</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50999,7 +50999,7 @@
         <v>45273</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45274</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>45274</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45282</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45282</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45282</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45301</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>45305</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45308</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45308</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45308</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>45315</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45315</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51733,14 +51733,14 @@
     <row r="887" ht="15" customHeight="1">
       <c r="A887" t="inlineStr">
         <is>
-          <t>A 3158-2024</t>
+          <t>A 3159-2024</t>
         </is>
       </c>
       <c r="B887" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H887" t="n">
         <v>0</v>
@@ -51797,7 +51797,7 @@
         <v>45316</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -51847,14 +51847,14 @@
     <row r="889" ht="15" customHeight="1">
       <c r="A889" t="inlineStr">
         <is>
-          <t>A 3159-2024</t>
+          <t>A 3158-2024</t>
         </is>
       </c>
       <c r="B889" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         </is>
       </c>
       <c r="G889" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H889" t="n">
         <v>0</v>
@@ -51911,7 +51911,7 @@
         <v>45316</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45317</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52018,14 +52018,14 @@
     <row r="892" ht="15" customHeight="1">
       <c r="A892" t="inlineStr">
         <is>
-          <t>A 3455-2024</t>
+          <t>A 3439-2024</t>
         </is>
       </c>
       <c r="B892" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         </is>
       </c>
       <c r="G892" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -52075,14 +52075,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 3439-2024</t>
+          <t>A 3455-2024</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -52139,7 +52139,7 @@
         <v>45320</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45320</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52246,14 +52246,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 3584-2024</t>
+          <t>A 3579-2024</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -52303,14 +52303,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 3554-2024</t>
+          <t>A 3584-2024</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -52367,7 +52367,7 @@
         <v>45320</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52417,14 +52417,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 3582-2024</t>
+          <t>A 3581-2024</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>2.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -52474,14 +52474,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 3585-2024</t>
+          <t>A 3554-2024</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -52531,14 +52531,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 3581-2024</t>
+          <t>A 3585-2024</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>8.800000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -52595,7 +52595,7 @@
         <v>45320</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52645,14 +52645,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 3579-2024</t>
+          <t>A 3582-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -52709,7 +52709,7 @@
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45322</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52823,7 +52823,7 @@
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -52885,7 +52885,7 @@
         <v>45324</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -52947,7 +52947,7 @@
         <v>45328</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45328</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>45329</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>45329</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53175,7 +53175,7 @@
         <v>45329</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53232,7 +53232,7 @@
         <v>45329</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53282,14 +53282,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 5334-2024</t>
+          <t>A 5335-2024</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -53339,14 +53339,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5337-2024</t>
+          <t>A 5334-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -53396,14 +53396,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 5282-2024</t>
+          <t>A 5337-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53453,14 +53453,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 5336-2024</t>
+          <t>A 5282-2024</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>0.3</v>
+        <v>6.6</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53510,14 +53510,14 @@
     <row r="918" ht="15" customHeight="1">
       <c r="A918" t="inlineStr">
         <is>
-          <t>A 5335-2024</t>
+          <t>A 5336-2024</t>
         </is>
       </c>
       <c r="B918" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         </is>
       </c>
       <c r="G918" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -53567,14 +53567,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 6202-2024</t>
+          <t>A 6207-2024</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -53624,14 +53624,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 6201-2024</t>
+          <t>A 6202-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -53681,14 +53681,14 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 6207-2024</t>
+          <t>A 6201-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z921"/>
+  <dimension ref="A1:Z924"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45187</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44208</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44742</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>44760</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44923</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44965</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44977</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44977</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45070</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45077</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43318</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>43322</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>43340</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>43340</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>43340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>43355</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>43355</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>43362</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>43368</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43376</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43377</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43383</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>43383</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>43384</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>43385</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>43391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>43402</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>43411</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>43411</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>43412</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>43416</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>43418</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>43418</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>43418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>43419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>43419</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>43419</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>43420</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>43423</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>43423</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43429</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43430</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43430</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43431</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43437</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43438</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43440</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43440</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43446</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43446</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43461</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43461</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43467</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43487</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43490</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43493</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43493</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43493</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>43494</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>43495</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>43495</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>43495</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>43495</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>43499</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43501</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>43503</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>43503</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43503</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>43504</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>43504</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>43504</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>43504</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>43509</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>43509</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>43510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>43516</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>43516</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>43516</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>43517</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>43524</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>43529</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>43529</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>43529</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>43530</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>43530</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>43535</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>43539</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>43541</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>43543</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>43543</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>43545</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>43551</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>43556</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43557</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43557</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43558</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43558</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43563</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>43566</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>43567</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>43567</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>43579</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>43579</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>43584</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43587</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43587</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>43599</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>43600</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43602</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43605</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43605</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>43607</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>43612</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43612</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>43619</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>43623</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>43634</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>43643</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>43648</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43650</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43650</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43650</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43650</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43650</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43654</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43656</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43657</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43663</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43664</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43678</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43689</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43690</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43691</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>43691</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43692</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>43692</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>43696</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>43697</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>43697</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>43704</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>43704</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>43710</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>43713</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>43713</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>43717</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>43720</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>43725</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43727</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>43727</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>43727</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>43742</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>43760</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43771</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43771</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43775</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43782</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43787</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43791</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>43791</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>43791</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>43791</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>43797</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>43797</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>43804</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>43805</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>43810</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>43810</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>43810</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>43810</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>43811</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>43815</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>43838</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>43838</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>43838</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>43838</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43841</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>43847</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>43858</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>43865</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>43868</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>43871</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>43882</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>43885</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>43886</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>43886</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>43889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>43889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43893</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>43893</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>43899</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>43901</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>43902</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>43902</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43903</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43908</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>43909</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>43909</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>43910</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>43922</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>43923</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>43937</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>43937</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43937</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43937</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43943</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43943</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43948</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43949</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43955</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43966</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43969</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43974</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43975</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43989</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43998</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44000</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44004</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44004</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44004</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44014</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44015</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44022</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44022</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44022</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44022</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44022</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44022</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44025</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44027</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44039</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44047</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44055</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44064</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44064</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44066</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44066</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44066</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44069</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44070</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44078</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44081</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44083</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44083</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44083</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44088</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44090</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>44099</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44100</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44103</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>44111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44118</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44119</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44126</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44133</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44133</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44138</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44138</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44145</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44146</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44159</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>44159</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44161</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44161</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44165</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>44165</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44166</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>44173</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44209</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44215</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44216</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44224</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44228</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44228</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44232</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44235</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>44236</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>44236</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44237</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44237</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44239</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44242</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44243</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44243</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44245</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>44250</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44250</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44250</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44265</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44266</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44271</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44272</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44273</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44273</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44273</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44273</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44275</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44278</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44284</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44284</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44285</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44287</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44293</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44297</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44299</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44302</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44302</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44305</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44308</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44316</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44319</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44322</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44323</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44328</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44333</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44337</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44340</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44343</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44344</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44353</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44353</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44353</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44353</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44354</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44355</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44356</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44358</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44358</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44358</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>44358</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44358</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44358</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44362</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44365</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44365</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44365</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44376</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44378</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44378</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44378</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>44378</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44378</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44379</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44386</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44386</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44389</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44389</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44392</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44396</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44397</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44400</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44406</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44406</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44414</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44414</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44414</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44414</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44417</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44425</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44428</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44432</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44432</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44433</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44435</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44441</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44447</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44449</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44454</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44455</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44455</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44455</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44455</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44456</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>44456</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>44456</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44459</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44462</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>44463</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44465</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>44467</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44467</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44469</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44469</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44473</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44473</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44474</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44488</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44488</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44489</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44489</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44489</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44495</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44495</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44496</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44496</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44497</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44498</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44502</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44507</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44508</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44516</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44522</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44523</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44523</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44523</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44529</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44530</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44544</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44544</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44547</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44550</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44551</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44551</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44551</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44551</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44551</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44553</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44558</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44558</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44558</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44563</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44563</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44571</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44575</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44575</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44578</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44578</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44585</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>44594</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44594</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44606</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44606</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44606</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44606</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44607</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44607</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44614</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44614</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44615</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44621</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44626</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44638</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44648</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44651</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44657</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44662</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44662</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44694</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44694</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44697</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44699</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44700</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44712</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44712</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44712</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>44712</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>44715</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44721</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>44729</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>44732</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44735</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44735</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>44735</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44739</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44739</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44739</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>44739</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>44748</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>44748</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44748</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44748</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44749</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>44749</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44753</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>44753</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44767</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>44771</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>44776</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>44776</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>44791</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44802</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>44802</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44802</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44802</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44802</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44802</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44806</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44806</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44809</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44809</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44810</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44810</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44812</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44812</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44817</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44817</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44818</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44819</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44820</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44824</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44824</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44840</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44840</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44840</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44840</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44840</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>44840</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>44845</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44853</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44853</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>44855</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44860</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44860</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44865</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44866</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44866</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44867</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44867</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44873</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>44873</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>44880</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>44887</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>44888</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44893</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44893</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44894</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44894</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44896</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44896</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44896</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44896</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>44902</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44903</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44903</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44903</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44907</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44908</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>44909</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44910</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44910</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44915</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44923</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44923</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>44923</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>44926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>44931</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>44931</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44931</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>44931</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44931</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44931</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44935</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44938</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44943</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44945</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44949</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44949</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>44950</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44951</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>44952</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44952</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>44958</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>44958</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>44961</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>44966</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>44966</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>44970</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44970</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44971</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>44971</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>44971</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>44972</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>44972</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>44974</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>44974</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44974</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>44974</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>44977</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>44986</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>44986</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44986</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>44986</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>44995</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45000</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>45002</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45008</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45008</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45008</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>45009</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45009</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45009</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45009</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>45012</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45012</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45012</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45012</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45026</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45027</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45027</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45042</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45042</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45042</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45051</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45051</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45054</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45054</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45062</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45075</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45077</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45078</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45084</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45089</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45089</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45089</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45091</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45091</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45092</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45093</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45093</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45093</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45093</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45095</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45096</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45096</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45096</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45097</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45097</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45097</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45097</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45097</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45097</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45098</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>45098</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>45098</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45099</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45100</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45100</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45100</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45100</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45103</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45103</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45103</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45104</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45104</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45105</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45110</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45110</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45110</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45110</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45112</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45112</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45113</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45113</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45113</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45117</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45118</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45118</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45119</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45120</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45125</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45131</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45133</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45135</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45140</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45153</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45154</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45154</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45155</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45155</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45159</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45159</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45159</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45161</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45161</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45163</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45163</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45163</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45163</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45166</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45167</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45167</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45169</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45170</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45174</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45174</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45175</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45175</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45176</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45176</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>45177</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45177</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45180</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45182</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45183</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45187</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45187</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45189</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45189</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>45189</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45190</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45190</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45190</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45191</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45191</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45191</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45191</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>45191</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45191</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45196</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45198</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45198</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45198</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45199</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45201</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45201</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45204</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45204</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45211</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45211</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45211</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45211</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45211</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45211</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45212</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45212</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45212</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45218</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45223</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45229</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45230</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45231</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45231</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45233</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45235</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45235</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45235</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45235</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45235</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45235</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45236</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45237</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45237</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45240</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45244</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45245</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45246</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45247</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45247</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45250</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45250</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45250</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45250</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45250</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45251</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45254</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45257</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45258</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45259</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45260</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45266</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45266</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
         <v>45270</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45271</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45273</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50828,7 +50828,7 @@
         <v>45273</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45273</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45273</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50999,7 +50999,7 @@
         <v>45273</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45274</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>45274</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45282</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45282</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45282</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45301</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>45305</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45308</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45308</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45308</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51619,14 +51619,14 @@
     <row r="885" ht="15" customHeight="1">
       <c r="A885" t="inlineStr">
         <is>
-          <t>A 2880-2024</t>
+          <t>A 2879-2024</t>
         </is>
       </c>
       <c r="B885" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -51676,14 +51676,14 @@
     <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
-          <t>A 2879-2024</t>
+          <t>A 2880-2024</t>
         </is>
       </c>
       <c r="B886" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H886" t="n">
         <v>0</v>
@@ -51740,7 +51740,7 @@
         <v>45316</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>45316</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -51854,7 +51854,7 @@
         <v>45316</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45316</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45317</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45320</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>45320</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45320</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45320</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52246,14 +52246,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 3579-2024</t>
+          <t>A 3584-2024</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -52303,14 +52303,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 3584-2024</t>
+          <t>A 3554-2024</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -52360,14 +52360,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 3553-2024</t>
+          <t>A 3579-2024</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -52417,14 +52417,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 3581-2024</t>
+          <t>A 3583-2024</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>8.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -52474,14 +52474,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 3554-2024</t>
+          <t>A 3582-2024</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -52531,14 +52531,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 3585-2024</t>
+          <t>A 3553-2024</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -52588,14 +52588,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 3583-2024</t>
+          <t>A 3581-2024</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>2.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -52645,14 +52645,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 3582-2024</t>
+          <t>A 3585-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -52709,7 +52709,7 @@
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45322</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52823,7 +52823,7 @@
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -52885,7 +52885,7 @@
         <v>45324</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -52947,7 +52947,7 @@
         <v>45328</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45328</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>45329</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53111,14 +53111,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 4991-2024</t>
+          <t>A 4990-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53168,14 +53168,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 4990-2024</t>
+          <t>A 4994-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53225,14 +53225,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 4994-2024</t>
+          <t>A 4991-2024</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         </is>
       </c>
       <c r="G913" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -53289,7 +53289,7 @@
         <v>45331</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53339,14 +53339,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5334-2024</t>
+          <t>A 5337-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -53396,14 +53396,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 5337-2024</t>
+          <t>A 5282-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53453,14 +53453,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 5282-2024</t>
+          <t>A 5336-2024</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>6.6</v>
+        <v>0.3</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53510,14 +53510,14 @@
     <row r="918" ht="15" customHeight="1">
       <c r="A918" t="inlineStr">
         <is>
-          <t>A 5336-2024</t>
+          <t>A 5334-2024</t>
         </is>
       </c>
       <c r="B918" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         </is>
       </c>
       <c r="G918" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -53574,7 +53574,7 @@
         <v>45337</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53631,7 +53631,7 @@
         <v>45337</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53678,7 +53678,7 @@
       </c>
       <c r="R920" s="2" t="inlineStr"/>
     </row>
-    <row r="921">
+    <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
           <t>A 6201-2024</t>
@@ -53688,7 +53688,7 @@
         <v>45337</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53734,6 +53734,187 @@
         <v>0</v>
       </c>
       <c r="R921" s="2" t="inlineStr"/>
+    </row>
+    <row r="922" ht="15" customHeight="1">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>A 6616-2024</t>
+        </is>
+      </c>
+      <c r="B922" s="1" t="n">
+        <v>45341</v>
+      </c>
+      <c r="C922" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>GISLAVED</t>
+        </is>
+      </c>
+      <c r="G922" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H922" t="n">
+        <v>0</v>
+      </c>
+      <c r="I922" t="n">
+        <v>0</v>
+      </c>
+      <c r="J922" t="n">
+        <v>0</v>
+      </c>
+      <c r="K922" t="n">
+        <v>0</v>
+      </c>
+      <c r="L922" t="n">
+        <v>0</v>
+      </c>
+      <c r="M922" t="n">
+        <v>0</v>
+      </c>
+      <c r="N922" t="n">
+        <v>0</v>
+      </c>
+      <c r="O922" t="n">
+        <v>0</v>
+      </c>
+      <c r="P922" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q922" t="n">
+        <v>0</v>
+      </c>
+      <c r="R922" s="2" t="inlineStr"/>
+    </row>
+    <row r="923" ht="15" customHeight="1">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>A 6774-2024</t>
+        </is>
+      </c>
+      <c r="B923" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C923" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>GISLAVED</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="G923" t="n">
+        <v>6</v>
+      </c>
+      <c r="H923" t="n">
+        <v>0</v>
+      </c>
+      <c r="I923" t="n">
+        <v>0</v>
+      </c>
+      <c r="J923" t="n">
+        <v>0</v>
+      </c>
+      <c r="K923" t="n">
+        <v>0</v>
+      </c>
+      <c r="L923" t="n">
+        <v>0</v>
+      </c>
+      <c r="M923" t="n">
+        <v>0</v>
+      </c>
+      <c r="N923" t="n">
+        <v>0</v>
+      </c>
+      <c r="O923" t="n">
+        <v>0</v>
+      </c>
+      <c r="P923" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q923" t="n">
+        <v>0</v>
+      </c>
+      <c r="R923" s="2" t="inlineStr"/>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>A 6776-2024</t>
+        </is>
+      </c>
+      <c r="B924" s="1" t="n">
+        <v>45342</v>
+      </c>
+      <c r="C924" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>GISLAVED</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="G924" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H924" t="n">
+        <v>0</v>
+      </c>
+      <c r="I924" t="n">
+        <v>0</v>
+      </c>
+      <c r="J924" t="n">
+        <v>0</v>
+      </c>
+      <c r="K924" t="n">
+        <v>0</v>
+      </c>
+      <c r="L924" t="n">
+        <v>0</v>
+      </c>
+      <c r="M924" t="n">
+        <v>0</v>
+      </c>
+      <c r="N924" t="n">
+        <v>0</v>
+      </c>
+      <c r="O924" t="n">
+        <v>0</v>
+      </c>
+      <c r="P924" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q924" t="n">
+        <v>0</v>
+      </c>
+      <c r="R924" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z924"/>
+  <dimension ref="A1:Z925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45187</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44208</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44742</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>44760</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44923</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44965</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44977</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44977</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45070</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45077</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43318</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>43322</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>43340</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>43340</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>43340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>43355</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>43355</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>43362</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>43368</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43376</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43377</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43383</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>43383</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>43384</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>43385</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>43391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>43402</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>43411</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>43411</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>43412</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>43416</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>43418</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>43418</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>43418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>43419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>43419</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>43419</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>43420</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>43423</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>43423</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43429</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43430</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43430</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43431</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43437</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43438</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43440</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43440</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43446</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43446</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43461</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43461</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43467</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43487</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43490</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43493</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43493</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43493</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>43494</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>43495</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>43495</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>43495</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>43495</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>43499</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43501</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>43503</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>43503</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43503</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>43504</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>43504</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>43504</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>43504</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>43509</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>43509</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>43510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>43516</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>43516</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>43516</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>43517</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>43524</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>43529</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>43529</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>43529</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>43530</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>43530</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>43535</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>43539</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>43541</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>43543</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>43543</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>43545</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>43551</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>43556</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43557</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43557</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43558</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43558</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43563</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>43566</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>43567</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>43567</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>43579</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>43579</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>43584</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43587</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43587</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>43599</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>43600</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43602</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43605</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43605</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>43607</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>43612</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43612</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>43619</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>43623</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>43634</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>43643</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>43648</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43650</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43650</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43650</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43650</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43650</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43654</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43656</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43657</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43663</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43664</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43678</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43689</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43690</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43691</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>43691</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43692</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>43692</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>43696</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>43697</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>43697</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>43704</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>43704</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>43710</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>43713</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>43713</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>43717</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>43720</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>43725</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43727</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>43727</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>43727</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>43742</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>43760</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43771</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43771</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43775</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43782</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43787</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43791</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>43791</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>43791</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>43791</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>43797</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>43797</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>43804</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>43805</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>43810</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>43810</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>43810</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>43810</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>43811</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>43815</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>43838</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>43838</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>43838</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>43838</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43841</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>43847</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>43858</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>43865</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>43868</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>43871</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>43882</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>43885</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>43886</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>43886</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>43889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>43889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43893</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>43893</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>43899</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>43901</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>43902</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>43902</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43903</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43908</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>43909</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>43909</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>43910</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>43922</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>43923</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>43937</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>43937</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43937</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43937</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43943</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43943</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43948</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43949</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43955</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43966</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43969</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43974</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43975</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43989</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43998</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44000</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44004</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44004</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44004</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44014</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44015</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44022</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44022</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44022</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44022</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44022</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44022</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44025</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44027</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44039</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44047</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44055</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44064</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44064</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44066</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44066</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44066</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44069</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44070</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44078</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44081</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44083</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44083</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44083</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44088</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44090</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>44099</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44100</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44103</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>44111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44118</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44119</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44126</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44133</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44133</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44138</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44138</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44145</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44146</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44159</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>44159</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44161</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44161</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44165</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>44165</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44166</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>44173</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44209</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44215</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44216</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44224</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44228</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44228</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44232</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44235</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>44236</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>44236</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44237</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44237</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44239</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44242</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44243</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44243</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44245</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>44250</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44250</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44250</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44265</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44266</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44271</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44272</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44273</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44273</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44273</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44273</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44275</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44278</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44284</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44284</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44285</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44287</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44293</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44297</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44299</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44302</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44302</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44305</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44308</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44316</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44319</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44322</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44323</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44328</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44333</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44337</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44340</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44343</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44344</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44353</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44353</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44353</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44353</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44354</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44355</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44356</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44358</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44358</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44358</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>44358</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44358</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44358</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44362</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44365</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44365</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44365</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44376</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44378</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44378</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44378</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>44378</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44378</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44379</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44386</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44386</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44389</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44389</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44392</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44396</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44397</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44400</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44406</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44406</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44414</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44414</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44414</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44414</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44417</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44425</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44428</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44432</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44432</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44433</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44435</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44441</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44447</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44449</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44454</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44455</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44455</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44455</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44455</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44456</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>44456</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>44456</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44459</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44462</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>44463</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44465</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>44467</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44467</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44469</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44469</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44473</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44473</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44474</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44488</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44488</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44489</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44489</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44489</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44495</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44495</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44496</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44496</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44497</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44498</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44502</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44507</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44508</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44516</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44522</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44523</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44523</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44523</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44529</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44530</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44544</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44544</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44547</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44550</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44551</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44551</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44551</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44551</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44551</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44553</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44558</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44558</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44558</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44563</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44563</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44571</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44575</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44575</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44578</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44578</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44585</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>44594</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44594</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44606</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44606</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44606</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44606</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44607</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44607</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44614</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44614</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44615</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44621</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44626</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44638</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44648</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44651</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44657</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44662</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44662</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44694</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44694</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44697</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44699</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44700</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44712</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44712</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44712</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>44712</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>44715</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44721</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>44729</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>44732</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44735</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44735</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>44735</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44739</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44739</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44739</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>44739</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>44748</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>44748</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44748</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44748</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44749</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>44749</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44753</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>44753</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44767</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>44771</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>44776</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>44776</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>44791</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44802</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>44802</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44802</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44802</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44802</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44802</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44806</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44806</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44809</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44809</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44810</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44810</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44812</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44812</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44817</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44817</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44818</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44819</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44820</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44824</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44824</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44840</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44840</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44840</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44840</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44840</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>44840</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>44845</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44853</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44853</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>44855</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44860</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44860</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44865</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44866</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44866</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44867</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44867</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44873</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>44873</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>44880</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>44887</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>44888</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44893</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44893</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44894</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44894</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44896</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44896</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44896</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44896</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>44902</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44903</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44903</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44903</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44907</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44908</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>44909</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44910</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44910</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44915</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44923</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44923</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>44923</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>44926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>44931</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>44931</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44931</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>44931</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44931</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44931</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44935</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44938</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44943</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44945</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44949</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44949</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>44950</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44951</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>44952</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44952</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>44958</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>44958</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>44961</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>44966</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>44966</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>44970</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44970</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44971</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>44971</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>44971</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>44972</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>44972</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>44974</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>44974</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44974</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>44974</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>44977</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>44986</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>44986</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44986</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>44986</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>44995</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45000</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>45002</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45008</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45008</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45008</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>45009</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45009</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45009</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45009</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>45012</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45012</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45012</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45012</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45026</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45027</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45027</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45042</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45042</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45042</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45051</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45051</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45054</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45054</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45062</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45075</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45077</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45078</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45084</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45089</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45089</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45089</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45091</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45091</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45092</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45093</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45093</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45093</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45093</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45095</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45096</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45096</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45096</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45097</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45097</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45097</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45097</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45097</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45097</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45098</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>45098</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>45098</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45099</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45100</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45100</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45100</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45100</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45103</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45103</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45103</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45104</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45104</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45105</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45110</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45110</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45110</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45110</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45112</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45112</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45113</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45113</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45113</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45117</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45118</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45118</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45119</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45120</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45125</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45131</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45133</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45135</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45140</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45153</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45154</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45154</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45155</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45155</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45159</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45159</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45159</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45161</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45161</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45163</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45163</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45163</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45163</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45166</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45167</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45167</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45169</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45170</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45174</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45174</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45175</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45175</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45176</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45176</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>45177</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45177</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45180</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45182</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45183</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45187</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45187</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45189</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45189</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>45189</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45190</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45190</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45190</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45191</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45191</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45191</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45191</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>45191</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45191</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45196</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45198</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45198</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45198</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45199</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45201</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45201</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45204</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45204</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45211</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45211</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45211</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45211</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45211</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45211</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45212</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45212</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45212</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45218</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45223</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45229</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45230</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45231</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45231</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45233</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45235</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45235</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45235</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45235</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45235</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45235</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45236</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45237</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45237</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45240</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45244</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45245</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45246</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45247</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45247</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45250</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45250</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45250</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45250</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45250</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45251</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45254</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45257</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45258</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45259</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45260</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45266</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45266</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
         <v>45270</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45271</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45273</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50828,7 +50828,7 @@
         <v>45273</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45273</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45273</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50999,7 +50999,7 @@
         <v>45273</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45274</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>45274</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45282</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45282</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45282</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45301</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>45305</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45308</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45308</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45308</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>45315</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45315</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51733,14 +51733,14 @@
     <row r="887" ht="15" customHeight="1">
       <c r="A887" t="inlineStr">
         <is>
-          <t>A 3159-2024</t>
+          <t>A 3154-2024</t>
         </is>
       </c>
       <c r="B887" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="H887" t="n">
         <v>0</v>
@@ -51790,14 +51790,14 @@
     <row r="888" ht="15" customHeight="1">
       <c r="A888" t="inlineStr">
         <is>
-          <t>A 3154-2024</t>
+          <t>A 3158-2024</t>
         </is>
       </c>
       <c r="B888" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         </is>
       </c>
       <c r="G888" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -51847,14 +51847,14 @@
     <row r="889" ht="15" customHeight="1">
       <c r="A889" t="inlineStr">
         <is>
-          <t>A 3158-2024</t>
+          <t>A 3159-2024</t>
         </is>
       </c>
       <c r="B889" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         </is>
       </c>
       <c r="G889" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H889" t="n">
         <v>0</v>
@@ -51911,7 +51911,7 @@
         <v>45316</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45317</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52018,14 +52018,14 @@
     <row r="892" ht="15" customHeight="1">
       <c r="A892" t="inlineStr">
         <is>
-          <t>A 3439-2024</t>
+          <t>A 3455-2024</t>
         </is>
       </c>
       <c r="B892" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         </is>
       </c>
       <c r="G892" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -52075,14 +52075,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 3455-2024</t>
+          <t>A 3553-2024</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -52132,14 +52132,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 3552-2024</t>
+          <t>A 3581-2024</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         </is>
       </c>
       <c r="G894" t="n">
-        <v>2.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -52189,14 +52189,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 3556-2024</t>
+          <t>A 3554-2024</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52246,14 +52246,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 3584-2024</t>
+          <t>A 3579-2024</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -52303,14 +52303,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 3554-2024</t>
+          <t>A 3583-2024</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -52360,14 +52360,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 3579-2024</t>
+          <t>A 3439-2024</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -52417,14 +52417,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 3583-2024</t>
+          <t>A 3552-2024</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -52474,14 +52474,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 3582-2024</t>
+          <t>A 3556-2024</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -52531,14 +52531,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 3553-2024</t>
+          <t>A 3584-2024</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -52588,14 +52588,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 3581-2024</t>
+          <t>A 3585-2024</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>8.800000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -52645,14 +52645,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 3585-2024</t>
+          <t>A 3582-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -52709,7 +52709,7 @@
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45322</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52816,14 +52816,14 @@
     <row r="906" ht="15" customHeight="1">
       <c r="A906" t="inlineStr">
         <is>
-          <t>A 4226-2024</t>
+          <t>A 4223-2024</t>
         </is>
       </c>
       <c r="B906" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -52841,7 +52841,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -52878,14 +52878,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 4223-2024</t>
+          <t>A 4226-2024</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         </is>
       </c>
       <c r="G907" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -52947,7 +52947,7 @@
         <v>45328</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45328</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53054,14 +53054,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 4992-2024</t>
+          <t>A 4990-2024</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53111,14 +53111,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 4990-2024</t>
+          <t>A 4994-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53168,14 +53168,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 4994-2024</t>
+          <t>A 4992-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53232,7 +53232,7 @@
         <v>45329</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53289,7 +53289,7 @@
         <v>45331</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53339,14 +53339,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5337-2024</t>
+          <t>A 5334-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -53396,14 +53396,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 5282-2024</t>
+          <t>A 5337-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53453,14 +53453,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 5336-2024</t>
+          <t>A 5282-2024</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>0.3</v>
+        <v>6.6</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53510,14 +53510,14 @@
     <row r="918" ht="15" customHeight="1">
       <c r="A918" t="inlineStr">
         <is>
-          <t>A 5334-2024</t>
+          <t>A 5336-2024</t>
         </is>
       </c>
       <c r="B918" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         </is>
       </c>
       <c r="G918" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -53567,14 +53567,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 6207-2024</t>
+          <t>A 6202-2024</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -53624,14 +53624,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 6202-2024</t>
+          <t>A 6207-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -53688,7 +53688,7 @@
         <v>45337</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53745,7 +53745,7 @@
         <v>45341</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>45342</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -53854,7 +53854,7 @@
       </c>
       <c r="R923" s="2" t="inlineStr"/>
     </row>
-    <row r="924">
+    <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
           <t>A 6776-2024</t>
@@ -53864,7 +53864,7 @@
         <v>45342</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -53915,6 +53915,63 @@
         <v>0</v>
       </c>
       <c r="R924" s="2" t="inlineStr"/>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>A 7029-2024</t>
+        </is>
+      </c>
+      <c r="B925" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C925" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>GISLAVED</t>
+        </is>
+      </c>
+      <c r="G925" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H925" t="n">
+        <v>0</v>
+      </c>
+      <c r="I925" t="n">
+        <v>0</v>
+      </c>
+      <c r="J925" t="n">
+        <v>0</v>
+      </c>
+      <c r="K925" t="n">
+        <v>0</v>
+      </c>
+      <c r="L925" t="n">
+        <v>0</v>
+      </c>
+      <c r="M925" t="n">
+        <v>0</v>
+      </c>
+      <c r="N925" t="n">
+        <v>0</v>
+      </c>
+      <c r="O925" t="n">
+        <v>0</v>
+      </c>
+      <c r="P925" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q925" t="n">
+        <v>0</v>
+      </c>
+      <c r="R925" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -569,7 +569,7 @@
         <v>45187</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44208</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44742</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>44760</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44923</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44965</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44977</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44977</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45070</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45077</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43318</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>43322</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>43340</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>43340</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>43340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>43355</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>43355</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>43362</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>43368</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43376</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43377</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43383</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>43383</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>43384</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>43385</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>43391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>43402</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>43411</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>43411</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>43412</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>43416</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>43418</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>43418</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>43418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>43419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>43419</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>43419</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>43420</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>43423</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>43423</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43429</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43430</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43430</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43431</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43437</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43438</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43440</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43440</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43446</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43446</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43461</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43461</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43467</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43487</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43490</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43493</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43493</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43493</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>43494</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>43495</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>43495</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>43495</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>43495</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>43499</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43501</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>43503</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>43503</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43503</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>43504</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>43504</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>43504</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>43504</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>43509</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>43509</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>43510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>43516</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>43516</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>43516</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>43517</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>43524</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>43529</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>43529</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>43529</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>43530</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>43530</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>43535</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>43539</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>43541</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>43543</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>43543</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>43545</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>43551</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>43556</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43557</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43557</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43558</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43558</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43563</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>43566</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>43567</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>43567</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>43579</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>43579</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>43584</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43587</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43587</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>43599</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>43600</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43602</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43605</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43605</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>43607</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>43612</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43612</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>43619</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>43623</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>43634</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>43643</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>43648</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43650</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43650</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43650</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43650</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43650</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43654</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43656</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43657</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43663</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43664</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43678</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43689</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43690</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43691</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>43691</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43692</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>43692</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>43696</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>43697</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>43697</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>43704</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>43704</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>43710</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>43713</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>43713</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>43717</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>43720</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>43725</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43727</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>43727</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>43727</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>43742</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>43760</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43771</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43771</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43775</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43782</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43787</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43791</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>43791</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>43791</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>43791</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>43797</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>43797</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>43804</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>43805</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>43810</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>43810</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>43810</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>43810</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>43811</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>43815</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>43838</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>43838</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>43838</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>43838</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43841</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>43847</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>43858</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>43865</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>43868</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>43871</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>43882</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>43885</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>43886</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>43886</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>43889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>43889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43893</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>43893</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>43899</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>43901</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>43902</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>43902</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43903</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43908</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>43909</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>43909</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>43910</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>43922</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>43923</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>43937</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>43937</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43937</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43937</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43943</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43943</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43948</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43949</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43955</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43966</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43969</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43974</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43975</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43989</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43998</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44000</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44004</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44004</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44004</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44014</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44015</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44022</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44022</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44022</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44022</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44022</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44022</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44025</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44027</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44039</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44047</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44055</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44064</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44064</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44066</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44066</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44066</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44069</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44070</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44078</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44081</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44083</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44083</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44083</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44088</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44090</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>44099</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44100</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44103</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>44111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44118</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44119</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44126</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44133</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44133</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44138</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44138</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44145</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44146</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44159</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>44159</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44161</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44161</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44165</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>44165</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44166</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>44173</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44209</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44215</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44216</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44224</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44228</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44228</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44232</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44235</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>44236</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>44236</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44237</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44237</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44239</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44242</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44243</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44243</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44245</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>44250</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44250</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44250</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44265</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44266</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44271</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44272</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44273</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44273</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44273</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44273</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44275</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44278</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44284</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44284</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44285</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44287</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44293</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44297</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44299</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44302</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44302</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44305</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44308</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44316</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44319</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44322</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44323</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44328</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44333</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44337</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44340</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44343</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44344</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44353</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44353</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44353</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44353</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44354</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44355</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44356</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44358</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44358</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44358</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>44358</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44358</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44358</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44362</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44365</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44365</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44365</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44376</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44378</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44378</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44378</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>44378</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44378</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44379</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44386</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44386</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44389</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44389</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44392</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44396</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44397</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44400</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44406</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44406</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44414</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44414</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44414</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44414</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44417</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44425</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44428</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44432</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44432</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44433</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44435</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44441</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44447</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44449</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44454</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44455</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44455</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44455</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44455</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44456</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>44456</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>44456</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44459</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44462</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>44463</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44465</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>44467</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44467</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44469</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44469</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44473</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44473</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44474</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44488</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44488</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44489</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44489</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44489</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44495</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44495</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44496</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44496</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44497</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44498</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44502</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44507</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44508</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44516</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44522</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44523</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44523</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44523</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44529</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44530</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44544</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44544</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44547</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44550</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44551</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44551</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44551</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44551</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44551</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44553</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44558</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44558</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44558</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44563</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44563</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44571</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44575</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44575</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44578</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44578</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44585</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>44594</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44594</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44606</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44606</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44606</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44606</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44607</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44607</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44614</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44614</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44615</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44621</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44626</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44638</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44648</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44651</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44657</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44662</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44662</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44694</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44694</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44697</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44699</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44700</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44712</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44712</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44712</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>44712</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>44715</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44721</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>44729</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>44732</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44735</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44735</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>44735</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44739</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44739</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44739</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>44739</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>44748</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>44748</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44748</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44748</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44749</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>44749</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44753</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>44753</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44767</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>44771</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>44776</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>44776</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>44791</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44802</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>44802</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44802</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44802</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44802</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44802</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44806</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44806</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44809</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44809</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44810</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44810</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44812</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44812</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44817</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44817</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44818</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44819</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44820</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44824</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44824</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44840</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44840</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44840</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44840</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44840</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>44840</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>44845</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44853</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44853</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>44855</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44860</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44860</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44865</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44866</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44866</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44867</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44867</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44873</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>44873</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>44880</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>44887</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>44888</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44893</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44893</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44894</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44894</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44896</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44896</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44896</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44896</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>44902</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44903</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44903</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44903</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44907</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44908</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>44909</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44910</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44910</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44915</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44923</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44923</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>44923</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>44926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>44931</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>44931</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44931</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>44931</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44931</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44931</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44935</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44938</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44943</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44945</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44949</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44949</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>44950</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44951</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>44952</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44952</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>44958</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>44958</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>44961</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>44966</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>44966</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>44970</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44970</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44971</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>44971</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>44971</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>44972</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>44972</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>44974</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>44974</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44974</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>44974</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>44977</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>44986</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>44986</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44986</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>44986</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>44995</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45000</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>45002</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45008</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45008</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45008</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>45009</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45009</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45009</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45009</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>45012</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45012</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45012</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45012</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45026</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45027</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45027</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45042</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45042</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45042</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45051</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45051</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45054</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45054</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45062</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45075</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45077</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45078</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45084</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45089</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45089</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45089</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45091</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45091</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45092</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45093</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45093</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45093</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45093</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45095</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45096</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45096</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45096</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45097</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45097</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45097</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45097</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45097</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45097</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45098</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>45098</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>45098</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45099</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45100</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45100</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45100</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45100</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45103</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45103</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45103</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45104</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45104</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45105</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45110</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45110</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45110</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45110</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45112</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45112</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45113</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45113</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45113</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45117</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45118</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45118</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45119</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45120</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45125</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45131</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45133</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45135</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45140</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45153</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45154</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45154</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45155</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45155</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45159</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45159</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45159</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45161</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45161</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45163</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45163</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45163</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45163</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45166</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45167</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45167</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45169</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45170</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45174</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45174</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45175</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45175</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45176</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45176</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>45177</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45177</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45180</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45182</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45183</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45187</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45187</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45189</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45189</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>45189</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45190</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45190</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45190</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45191</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45191</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45191</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45191</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>45191</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45191</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45196</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45198</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45198</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45198</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45199</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45201</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45201</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45204</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45204</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45211</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45211</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45211</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45211</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45211</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45211</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45212</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45212</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45212</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45218</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45223</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45229</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45230</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45231</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45231</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45233</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45235</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45235</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45235</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45235</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45235</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45235</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45236</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45237</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45237</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45240</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45244</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45245</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45246</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45247</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45247</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45250</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45250</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45250</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45250</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45250</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45251</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45254</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45257</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45258</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45259</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45260</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45266</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45266</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
         <v>45270</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45271</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45273</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50828,7 +50828,7 @@
         <v>45273</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45273</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45273</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50999,7 +50999,7 @@
         <v>45273</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45274</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>45274</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45282</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45282</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45282</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45301</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>45305</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45308</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45308</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45308</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>45315</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45315</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51733,14 +51733,14 @@
     <row r="887" ht="15" customHeight="1">
       <c r="A887" t="inlineStr">
         <is>
-          <t>A 3154-2024</t>
+          <t>A 3159-2024</t>
         </is>
       </c>
       <c r="B887" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="H887" t="n">
         <v>0</v>
@@ -51790,14 +51790,14 @@
     <row r="888" ht="15" customHeight="1">
       <c r="A888" t="inlineStr">
         <is>
-          <t>A 3158-2024</t>
+          <t>A 3154-2024</t>
         </is>
       </c>
       <c r="B888" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         </is>
       </c>
       <c r="G888" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -51847,14 +51847,14 @@
     <row r="889" ht="15" customHeight="1">
       <c r="A889" t="inlineStr">
         <is>
-          <t>A 3159-2024</t>
+          <t>A 3158-2024</t>
         </is>
       </c>
       <c r="B889" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         </is>
       </c>
       <c r="G889" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H889" t="n">
         <v>0</v>
@@ -51911,7 +51911,7 @@
         <v>45316</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45317</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45320</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>45320</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45320</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52189,14 +52189,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 3554-2024</t>
+          <t>A 3439-2024</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52246,14 +52246,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 3579-2024</t>
+          <t>A 3552-2024</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -52303,14 +52303,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 3583-2024</t>
+          <t>A 3556-2024</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -52360,14 +52360,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 3439-2024</t>
+          <t>A 3584-2024</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -52417,14 +52417,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 3552-2024</t>
+          <t>A 3579-2024</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -52474,14 +52474,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 3556-2024</t>
+          <t>A 3583-2024</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -52531,14 +52531,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 3584-2024</t>
+          <t>A 3554-2024</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -52588,14 +52588,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 3585-2024</t>
+          <t>A 3582-2024</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -52645,14 +52645,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 3582-2024</t>
+          <t>A 3585-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -52709,7 +52709,7 @@
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45322</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52823,7 +52823,7 @@
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -52885,7 +52885,7 @@
         <v>45324</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -52947,7 +52947,7 @@
         <v>45328</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45328</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53054,14 +53054,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 4990-2024</t>
+          <t>A 4991-2024</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53111,14 +53111,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 4994-2024</t>
+          <t>A 4990-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53168,14 +53168,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 4992-2024</t>
+          <t>A 4994-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53225,14 +53225,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 4991-2024</t>
+          <t>A 4992-2024</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53289,7 +53289,7 @@
         <v>45331</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53339,14 +53339,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5334-2024</t>
+          <t>A 5337-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -53396,14 +53396,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 5337-2024</t>
+          <t>A 5334-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53460,7 +53460,7 @@
         <v>45331</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53517,7 +53517,7 @@
         <v>45331</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53567,14 +53567,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 6202-2024</t>
+          <t>A 6201-2024</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -53624,14 +53624,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 6207-2024</t>
+          <t>A 6202-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -53681,14 +53681,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 6201-2024</t>
+          <t>A 6207-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -53745,7 +53745,7 @@
         <v>45341</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>45342</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45342</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45343</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z925"/>
+  <dimension ref="A1:Z927"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45187</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44208</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44742</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>44760</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44923</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44965</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44977</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44977</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45070</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45077</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43318</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>43322</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>43340</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>43340</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>43340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>43355</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>43355</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>43362</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>43368</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43376</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43377</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43383</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>43383</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>43384</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>43385</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>43391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>43402</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>43411</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>43411</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>43412</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>43416</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>43418</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>43418</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>43418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>43419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>43419</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>43419</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>43420</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>43423</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>43423</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43429</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43430</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43430</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43431</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43437</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43438</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43440</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43440</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43446</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43446</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43461</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43461</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43467</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43487</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43490</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43493</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43493</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43493</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>43494</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>43495</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>43495</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>43495</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>43495</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>43499</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43501</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>43503</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>43503</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43503</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>43504</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>43504</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>43504</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>43504</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>43509</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>43509</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>43510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>43516</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>43516</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>43516</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>43517</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>43524</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>43529</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>43529</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>43529</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>43530</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>43530</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>43535</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>43539</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>43541</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>43543</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>43543</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>43545</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>43551</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>43556</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43557</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43557</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43558</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43558</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43563</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>43566</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>43567</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>43567</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>43579</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>43579</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>43584</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43587</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43587</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>43599</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>43600</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43602</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43605</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43605</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>43607</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>43612</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43612</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>43619</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>43623</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>43634</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>43643</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>43648</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43650</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43650</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43650</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43650</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43650</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43654</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43656</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43657</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43663</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43664</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43678</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43689</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43690</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43691</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>43691</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43692</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>43692</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>43696</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>43697</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>43697</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>43704</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>43704</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>43710</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>43713</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>43713</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>43717</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>43720</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>43725</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43727</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>43727</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>43727</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>43742</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>43760</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43771</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43771</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43775</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43782</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43787</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43791</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>43791</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>43791</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>43791</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>43797</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>43797</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>43804</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>43805</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>43810</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>43810</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>43810</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>43810</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>43811</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>43815</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>43838</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>43838</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>43838</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>43838</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43841</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>43847</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>43858</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>43865</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>43868</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>43871</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>43882</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>43885</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>43886</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>43886</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>43889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>43889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43893</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>43893</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>43899</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>43901</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>43902</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>43902</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43903</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43908</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>43909</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>43909</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>43910</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>43922</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>43923</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>43937</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>43937</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43937</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43937</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43943</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43943</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43948</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43949</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43955</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43966</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43969</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43974</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43975</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43989</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43998</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44000</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44004</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44004</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44004</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44014</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44015</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44022</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44022</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44022</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44022</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44022</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44022</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44025</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44027</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44039</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44047</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44055</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44064</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44064</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44066</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44066</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44066</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44069</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44070</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44078</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44081</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44083</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44083</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44083</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44088</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44090</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>44099</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44100</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44103</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>44111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44118</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44119</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44126</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44133</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44133</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44138</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44138</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44145</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44146</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44159</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>44159</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44161</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44161</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44165</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>44165</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44166</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>44173</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44209</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44215</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44216</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44224</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44228</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44228</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44232</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44235</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>44236</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>44236</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44237</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44237</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44239</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44242</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44243</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44243</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44245</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>44250</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44250</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44250</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44265</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44266</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44271</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44272</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44273</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44273</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44273</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44273</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44275</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44278</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44284</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44284</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44285</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44287</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44293</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44297</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44299</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44302</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44302</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44305</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44308</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44316</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44319</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44322</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44323</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44328</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44333</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44337</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44340</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44343</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44344</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44353</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44353</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44353</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44353</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44354</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44355</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44356</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44358</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44358</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44358</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>44358</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44358</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44358</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44362</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44365</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44365</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44365</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44376</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44378</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44378</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44378</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>44378</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44378</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44379</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44386</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44386</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44389</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44389</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44392</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44396</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44397</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44400</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44406</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44406</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44414</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44414</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44414</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44414</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44417</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44425</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44428</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44432</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44432</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44433</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44435</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44441</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44447</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44449</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44454</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44455</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44455</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44455</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44455</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44456</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>44456</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>44456</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44459</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44462</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>44463</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44465</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>44467</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44467</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44469</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44469</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44473</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44473</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44474</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44488</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44488</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44489</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44489</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44489</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44495</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44495</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44496</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44496</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44497</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44498</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44502</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44507</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44508</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44516</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44522</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44523</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44523</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44523</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44529</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44530</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44544</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44544</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44547</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44550</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44551</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44551</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44551</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44551</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44551</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44553</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44558</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44558</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44558</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44563</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44563</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44571</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44575</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44575</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44578</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44578</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44585</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>44594</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44594</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44606</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44606</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44606</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44606</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44607</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44607</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44614</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44614</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44615</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44621</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44626</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44638</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44648</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44651</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44657</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44662</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44662</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44694</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44694</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44697</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44699</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44700</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44712</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44712</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44712</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>44712</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>44715</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44721</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>44729</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>44732</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44735</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44735</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>44735</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44739</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44739</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44739</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>44739</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>44748</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>44748</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44748</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44748</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44749</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>44749</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44753</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>44753</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44767</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>44771</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>44776</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>44776</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>44791</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44802</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>44802</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44802</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44802</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44802</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44802</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44806</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44806</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44809</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44809</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44810</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44810</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44812</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44812</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44817</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44817</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44818</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44819</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44820</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44824</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44824</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44840</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44840</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44840</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44840</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44840</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>44840</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>44845</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44853</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44853</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>44855</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44860</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44860</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44865</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44866</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44866</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44867</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44867</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44873</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>44873</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>44880</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>44887</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>44888</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44893</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44893</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44894</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44894</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44896</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44896</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44896</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44896</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>44902</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44903</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44903</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44903</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44907</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44908</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>44909</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44910</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44910</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44915</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44923</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44923</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>44923</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>44926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>44931</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>44931</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44931</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>44931</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44931</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44931</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44935</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44938</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44943</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44945</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44949</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44949</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>44950</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44951</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>44952</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44952</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>44958</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>44958</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>44961</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>44966</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>44966</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>44970</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44970</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44971</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>44971</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>44971</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>44972</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>44972</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>44974</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>44974</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44974</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>44974</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>44977</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>44986</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>44986</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44986</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>44986</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>44995</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45000</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>45002</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45008</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45008</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45008</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>45009</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45009</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45009</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45009</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>45012</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45012</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45012</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45012</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45026</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45027</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45027</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45042</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45042</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45042</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45051</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45051</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45054</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45054</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45062</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45075</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45077</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45078</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45084</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45089</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45089</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45089</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45091</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45091</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45092</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45093</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45093</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45093</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45093</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45095</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45096</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45096</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45096</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45097</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45097</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45097</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45097</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45097</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45097</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45098</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>45098</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>45098</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45099</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45100</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45100</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45100</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45100</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45103</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45103</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45103</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45104</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45104</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45105</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45110</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45110</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45110</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45110</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45112</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45112</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45113</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45113</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45113</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45117</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45118</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45118</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45119</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45120</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45125</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45131</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45133</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45135</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45140</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45153</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45154</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45154</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45155</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45155</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45159</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45159</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45159</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45161</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45161</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45163</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45163</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45163</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45163</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45166</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45167</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45167</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45169</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45170</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45174</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45174</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45175</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45175</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45176</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45176</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>45177</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45177</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45180</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45182</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45183</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45187</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45187</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45189</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45189</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>45189</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45190</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45190</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45190</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45191</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45191</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45191</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45191</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>45191</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45191</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45196</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45198</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45198</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45198</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45199</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45201</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45201</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45204</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45204</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45211</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45211</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45211</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45211</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45211</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45211</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45212</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45212</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45212</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45218</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45223</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45229</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45230</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45231</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45231</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45233</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45235</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45235</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45235</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45235</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45235</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45235</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45236</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45237</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45237</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45240</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45244</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45245</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45246</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45247</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45247</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45250</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45250</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45250</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45250</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45250</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45251</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45254</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45257</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45258</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45259</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45260</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45266</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45266</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
         <v>45270</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45271</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45273</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50828,7 +50828,7 @@
         <v>45273</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45273</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45273</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50999,7 +50999,7 @@
         <v>45273</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45274</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>45274</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45282</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45282</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45282</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45301</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>45305</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45308</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45308</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45308</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51619,14 +51619,14 @@
     <row r="885" ht="15" customHeight="1">
       <c r="A885" t="inlineStr">
         <is>
-          <t>A 2879-2024</t>
+          <t>A 2880-2024</t>
         </is>
       </c>
       <c r="B885" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -51676,14 +51676,14 @@
     <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
-          <t>A 2880-2024</t>
+          <t>A 2879-2024</t>
         </is>
       </c>
       <c r="B886" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H886" t="n">
         <v>0</v>
@@ -51733,14 +51733,14 @@
     <row r="887" ht="15" customHeight="1">
       <c r="A887" t="inlineStr">
         <is>
-          <t>A 3159-2024</t>
+          <t>A 3161-2024</t>
         </is>
       </c>
       <c r="B887" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H887" t="n">
         <v>0</v>
@@ -51797,7 +51797,7 @@
         <v>45316</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -51854,7 +51854,7 @@
         <v>45316</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -51904,14 +51904,14 @@
     <row r="890" ht="15" customHeight="1">
       <c r="A890" t="inlineStr">
         <is>
-          <t>A 3161-2024</t>
+          <t>A 3159-2024</t>
         </is>
       </c>
       <c r="B890" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         </is>
       </c>
       <c r="G890" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -51968,7 +51968,7 @@
         <v>45317</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45320</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52075,14 +52075,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 3553-2024</t>
+          <t>A 3439-2024</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -52132,14 +52132,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 3581-2024</t>
+          <t>A 3554-2024</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         </is>
       </c>
       <c r="G894" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -52189,14 +52189,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 3439-2024</t>
+          <t>A 3552-2024</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52246,14 +52246,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 3552-2024</t>
+          <t>A 3556-2024</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -52303,14 +52303,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 3556-2024</t>
+          <t>A 3584-2024</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -52360,14 +52360,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 3584-2024</t>
+          <t>A 3579-2024</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -52417,14 +52417,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 3579-2024</t>
+          <t>A 3583-2024</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -52474,14 +52474,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 3583-2024</t>
+          <t>A 3553-2024</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -52531,14 +52531,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 3554-2024</t>
+          <t>A 3581-2024</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -52595,7 +52595,7 @@
         <v>45320</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45320</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45322</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52816,14 +52816,14 @@
     <row r="906" ht="15" customHeight="1">
       <c r="A906" t="inlineStr">
         <is>
-          <t>A 4223-2024</t>
+          <t>A 4226-2024</t>
         </is>
       </c>
       <c r="B906" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -52841,7 +52841,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -52878,14 +52878,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 4226-2024</t>
+          <t>A 4223-2024</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         </is>
       </c>
       <c r="G907" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -52947,7 +52947,7 @@
         <v>45328</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45328</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53054,14 +53054,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 4991-2024</t>
+          <t>A 4990-2024</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53111,14 +53111,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 4990-2024</t>
+          <t>A 4994-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53168,14 +53168,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 4994-2024</t>
+          <t>A 4991-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53232,7 +53232,7 @@
         <v>45329</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53282,14 +53282,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 5335-2024</t>
+          <t>A 5282-2024</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -53339,14 +53339,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5337-2024</t>
+          <t>A 5336-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -53396,14 +53396,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 5334-2024</t>
+          <t>A 5335-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53453,14 +53453,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 5282-2024</t>
+          <t>A 5334-2024</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53510,14 +53510,14 @@
     <row r="918" ht="15" customHeight="1">
       <c r="A918" t="inlineStr">
         <is>
-          <t>A 5336-2024</t>
+          <t>A 5337-2024</t>
         </is>
       </c>
       <c r="B918" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         </is>
       </c>
       <c r="G918" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -53574,7 +53574,7 @@
         <v>45337</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53624,14 +53624,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 6202-2024</t>
+          <t>A 6207-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -53681,14 +53681,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 6207-2024</t>
+          <t>A 6202-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -53745,7 +53745,7 @@
         <v>45341</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>45342</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45342</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
       </c>
       <c r="R924" s="2" t="inlineStr"/>
     </row>
-    <row r="925">
+    <row r="925" ht="15" customHeight="1">
       <c r="A925" t="inlineStr">
         <is>
           <t>A 7029-2024</t>
@@ -53926,7 +53926,7 @@
         <v>45343</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -53972,6 +53972,120 @@
         <v>0</v>
       </c>
       <c r="R925" s="2" t="inlineStr"/>
+    </row>
+    <row r="926" ht="15" customHeight="1">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>A 7369-2024</t>
+        </is>
+      </c>
+      <c r="B926" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C926" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>GISLAVED</t>
+        </is>
+      </c>
+      <c r="G926" t="n">
+        <v>1</v>
+      </c>
+      <c r="H926" t="n">
+        <v>0</v>
+      </c>
+      <c r="I926" t="n">
+        <v>0</v>
+      </c>
+      <c r="J926" t="n">
+        <v>0</v>
+      </c>
+      <c r="K926" t="n">
+        <v>0</v>
+      </c>
+      <c r="L926" t="n">
+        <v>0</v>
+      </c>
+      <c r="M926" t="n">
+        <v>0</v>
+      </c>
+      <c r="N926" t="n">
+        <v>0</v>
+      </c>
+      <c r="O926" t="n">
+        <v>0</v>
+      </c>
+      <c r="P926" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q926" t="n">
+        <v>0</v>
+      </c>
+      <c r="R926" s="2" t="inlineStr"/>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>A 7367-2024</t>
+        </is>
+      </c>
+      <c r="B927" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C927" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>GISLAVED</t>
+        </is>
+      </c>
+      <c r="G927" t="n">
+        <v>1</v>
+      </c>
+      <c r="H927" t="n">
+        <v>0</v>
+      </c>
+      <c r="I927" t="n">
+        <v>0</v>
+      </c>
+      <c r="J927" t="n">
+        <v>0</v>
+      </c>
+      <c r="K927" t="n">
+        <v>0</v>
+      </c>
+      <c r="L927" t="n">
+        <v>0</v>
+      </c>
+      <c r="M927" t="n">
+        <v>0</v>
+      </c>
+      <c r="N927" t="n">
+        <v>0</v>
+      </c>
+      <c r="O927" t="n">
+        <v>0</v>
+      </c>
+      <c r="P927" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q927" t="n">
+        <v>0</v>
+      </c>
+      <c r="R927" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -569,7 +569,7 @@
         <v>45187</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44208</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44742</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>44760</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44923</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44965</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44977</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44977</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45070</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45077</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43318</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>43322</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>43340</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>43340</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>43340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>43355</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>43355</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>43362</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>43368</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43376</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43377</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43383</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>43383</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>43384</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>43385</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>43391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>43402</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>43411</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>43411</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>43412</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>43416</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>43418</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>43418</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>43418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>43419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>43419</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>43419</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>43420</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>43423</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>43423</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43429</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43430</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43430</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43431</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43437</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43438</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43440</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43440</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43446</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43446</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43461</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43461</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43467</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43487</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43490</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43493</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43493</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43493</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>43494</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>43495</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>43495</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>43495</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>43495</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>43499</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43501</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>43503</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>43503</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43503</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>43504</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>43504</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>43504</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>43504</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>43509</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>43509</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>43510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>43516</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>43516</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>43516</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>43517</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>43524</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>43529</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>43529</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>43529</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>43530</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>43530</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>43535</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>43539</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>43541</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>43543</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>43543</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>43545</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>43551</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>43556</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43557</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43557</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43558</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43558</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43563</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>43566</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>43567</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>43567</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>43579</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>43579</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>43584</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43587</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43587</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>43599</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>43600</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43602</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43605</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43605</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>43607</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>43612</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43612</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>43619</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>43623</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>43634</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>43643</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>43648</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43650</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43650</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43650</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43650</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43650</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43654</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43656</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43657</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43663</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43664</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43678</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43689</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43690</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43691</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>43691</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43692</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>43692</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>43696</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>43697</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>43697</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>43704</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>43704</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>43710</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>43713</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>43713</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>43717</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>43720</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>43725</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43727</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>43727</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>43727</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>43742</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>43760</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43771</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43771</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43775</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43782</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43787</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43791</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>43791</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>43791</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>43791</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>43797</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>43797</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>43804</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>43805</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>43810</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>43810</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>43810</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>43810</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>43811</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>43815</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>43838</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>43838</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>43838</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>43838</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43841</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>43847</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>43858</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>43865</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>43868</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>43871</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>43882</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>43885</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>43886</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>43886</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>43889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>43889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43893</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>43893</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>43899</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>43901</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>43902</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>43902</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43903</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43908</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>43909</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>43909</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>43910</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>43922</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>43923</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>43937</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>43937</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43937</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43937</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43943</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43943</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43948</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43949</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43955</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43966</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43969</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43974</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43975</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43989</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43998</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44000</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44004</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44004</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44004</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44014</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44015</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44022</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44022</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44022</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44022</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44022</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44022</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44025</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44027</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44039</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44047</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44055</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44064</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44064</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44066</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44066</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44066</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44069</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44070</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44078</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44081</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44083</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44083</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44083</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44088</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44090</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>44099</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44100</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44103</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>44111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44118</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44119</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44126</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44133</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44133</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44138</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44138</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44145</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44146</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44159</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>44159</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44161</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44161</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44165</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>44165</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44166</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>44173</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44209</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44215</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44216</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44224</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44228</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44228</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44232</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44235</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>44236</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>44236</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44237</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44237</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44239</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44242</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44243</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44243</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44245</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>44250</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44250</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44250</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44265</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44266</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44271</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44272</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44273</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44273</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44273</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44273</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44275</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44278</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44284</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44284</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44285</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44287</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44293</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44297</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44299</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44302</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44302</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44305</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44308</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44316</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44319</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44322</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44323</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44328</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44333</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44337</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44340</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44343</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44344</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44353</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44353</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44353</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44353</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44354</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44355</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44356</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44358</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44358</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44358</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>44358</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44358</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44358</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44362</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44365</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44365</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44365</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44376</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44378</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44378</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44378</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>44378</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44378</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44379</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44386</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44386</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44389</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44389</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44392</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44396</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44397</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44400</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44406</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44406</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44414</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44414</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44414</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44414</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44417</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44425</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44428</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44432</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44432</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44433</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44435</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44441</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44447</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44449</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44454</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44455</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44455</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44455</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44455</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44456</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>44456</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>44456</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44459</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44462</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>44463</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44465</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>44467</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44467</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44469</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44469</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44473</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44473</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44474</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44488</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44488</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44489</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44489</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44489</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44495</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44495</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44496</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44496</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44497</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44498</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44502</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44507</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44508</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44516</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44522</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44523</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44523</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44523</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44529</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44530</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44544</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44544</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44547</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44550</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44551</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44551</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44551</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44551</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44551</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44553</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44558</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44558</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44558</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44563</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44563</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44571</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44575</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44575</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44578</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44578</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44585</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>44594</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44594</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44606</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44606</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44606</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44606</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44607</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44607</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44614</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44614</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44615</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44621</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44626</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44638</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44648</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44651</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44657</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44662</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44662</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44694</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44694</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44697</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44699</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44700</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44712</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44712</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44712</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>44712</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>44715</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44721</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>44729</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>44732</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44735</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44735</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>44735</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44739</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44739</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44739</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>44739</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>44748</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>44748</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44748</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44748</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44749</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>44749</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44753</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>44753</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44767</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>44771</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>44776</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>44776</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>44791</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44802</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>44802</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44802</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44802</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44802</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44802</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44806</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44806</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44809</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44809</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44810</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44810</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44812</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44812</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44817</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44817</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44818</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44819</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44820</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44824</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44824</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44840</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44840</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44840</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44840</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44840</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>44840</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>44845</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44853</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44853</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>44855</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44860</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44860</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44865</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44866</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44866</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44867</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44867</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44873</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>44873</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>44880</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>44887</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>44888</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44893</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44893</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44894</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44894</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44896</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44896</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44896</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44896</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>44902</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44903</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44903</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44903</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44907</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44908</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>44909</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44910</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44910</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44915</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44923</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44923</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>44923</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>44926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>44931</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>44931</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44931</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>44931</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44931</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44931</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44935</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44938</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44943</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44945</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44949</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44949</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>44950</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44951</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>44952</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44952</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>44958</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>44958</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>44961</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>44966</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>44966</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>44970</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44970</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44971</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>44971</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>44971</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>44972</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>44972</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>44974</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>44974</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44974</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>44974</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>44977</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>44986</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>44986</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44986</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>44986</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>44995</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45000</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>45002</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45008</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45008</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45008</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>45009</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45009</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45009</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45009</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>45012</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45012</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45012</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45012</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45026</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45027</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45027</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45042</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45042</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45042</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45051</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45051</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45054</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45054</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45062</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45075</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45077</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45078</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45084</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45089</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45089</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45089</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45091</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45091</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45092</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45093</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45093</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45093</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45093</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45095</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45096</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45096</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45096</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45097</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45097</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45097</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45097</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45097</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45097</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45098</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>45098</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>45098</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45099</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45100</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45100</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45100</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45100</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45103</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45103</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45103</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45104</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45104</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45105</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45110</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45110</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45110</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45110</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45112</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45112</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45113</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45113</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45113</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45117</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45118</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45118</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45119</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45120</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45125</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45131</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45133</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45135</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45140</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45153</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45154</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45154</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45155</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45155</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45159</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45159</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45159</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45161</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45161</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45163</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45163</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45163</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45163</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45166</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45167</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45167</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45169</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45170</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45174</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45174</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45175</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45175</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45176</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45176</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>45177</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45177</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45180</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45182</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45183</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45187</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45187</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45189</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45189</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>45189</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45190</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45190</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45190</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45191</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45191</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45191</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45191</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>45191</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45191</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45196</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45198</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45198</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45198</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45199</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45201</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45201</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45204</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45204</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45211</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45211</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45211</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45211</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45211</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45211</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45212</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45212</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45212</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45218</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45223</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45229</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45230</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45231</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45231</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45233</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45235</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45235</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45235</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45235</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45235</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45235</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45236</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45237</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45237</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45240</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45244</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45245</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45246</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45247</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45247</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45250</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45250</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45250</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45250</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45250</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45251</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45254</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45257</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45258</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45259</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45260</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45266</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45266</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
         <v>45270</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45271</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45273</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50828,7 +50828,7 @@
         <v>45273</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45273</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45273</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50999,7 +50999,7 @@
         <v>45273</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45274</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>45274</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45282</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45282</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45282</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45301</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>45305</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45308</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45308</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45308</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>45315</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45315</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>45316</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>45316</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -51854,7 +51854,7 @@
         <v>45316</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45316</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45317</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52018,14 +52018,14 @@
     <row r="892" ht="15" customHeight="1">
       <c r="A892" t="inlineStr">
         <is>
-          <t>A 3455-2024</t>
+          <t>A 3439-2024</t>
         </is>
       </c>
       <c r="B892" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         </is>
       </c>
       <c r="G892" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -52075,14 +52075,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 3439-2024</t>
+          <t>A 3552-2024</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -52132,14 +52132,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 3554-2024</t>
+          <t>A 3579-2024</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         </is>
       </c>
       <c r="G894" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -52189,14 +52189,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 3552-2024</t>
+          <t>A 3583-2024</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52246,14 +52246,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 3556-2024</t>
+          <t>A 3455-2024</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -52303,14 +52303,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 3584-2024</t>
+          <t>A 3553-2024</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -52360,14 +52360,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 3579-2024</t>
+          <t>A 3581-2024</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>3.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -52417,14 +52417,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 3583-2024</t>
+          <t>A 3585-2024</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -52474,14 +52474,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 3553-2024</t>
+          <t>A 3554-2024</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -52531,14 +52531,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 3581-2024</t>
+          <t>A 3582-2024</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>8.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -52588,14 +52588,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 3582-2024</t>
+          <t>A 3584-2024</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -52645,14 +52645,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 3585-2024</t>
+          <t>A 3556-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -52702,14 +52702,14 @@
     <row r="904" ht="15" customHeight="1">
       <c r="A904" t="inlineStr">
         <is>
-          <t>A 3899-2024</t>
+          <t>A 3975-2024</t>
         </is>
       </c>
       <c r="B904" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         </is>
       </c>
       <c r="G904" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -52759,14 +52759,14 @@
     <row r="905" ht="15" customHeight="1">
       <c r="A905" t="inlineStr">
         <is>
-          <t>A 3975-2024</t>
+          <t>A 3899-2024</t>
         </is>
       </c>
       <c r="B905" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         </is>
       </c>
       <c r="G905" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -52816,14 +52816,14 @@
     <row r="906" ht="15" customHeight="1">
       <c r="A906" t="inlineStr">
         <is>
-          <t>A 4226-2024</t>
+          <t>A 4223-2024</t>
         </is>
       </c>
       <c r="B906" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -52841,7 +52841,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -52878,14 +52878,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 4223-2024</t>
+          <t>A 4226-2024</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         </is>
       </c>
       <c r="G907" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -52947,7 +52947,7 @@
         <v>45328</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45328</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53054,14 +53054,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 4990-2024</t>
+          <t>A 4991-2024</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53111,14 +53111,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 4994-2024</t>
+          <t>A 4990-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53168,14 +53168,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 4991-2024</t>
+          <t>A 4994-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53232,7 +53232,7 @@
         <v>45329</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53282,14 +53282,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 5282-2024</t>
+          <t>A 5337-2024</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -53339,14 +53339,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5336-2024</t>
+          <t>A 5334-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -53403,7 +53403,7 @@
         <v>45331</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53453,14 +53453,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 5334-2024</t>
+          <t>A 5282-2024</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53510,14 +53510,14 @@
     <row r="918" ht="15" customHeight="1">
       <c r="A918" t="inlineStr">
         <is>
-          <t>A 5337-2024</t>
+          <t>A 5336-2024</t>
         </is>
       </c>
       <c r="B918" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         </is>
       </c>
       <c r="G918" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -53567,14 +53567,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 6201-2024</t>
+          <t>A 6207-2024</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -53624,14 +53624,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 6207-2024</t>
+          <t>A 6201-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -53688,7 +53688,7 @@
         <v>45337</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53745,7 +53745,7 @@
         <v>45341</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -53795,14 +53795,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 6774-2024</t>
+          <t>A 6776-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -53857,14 +53857,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 6776-2024</t>
+          <t>A 6774-2024</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -53882,7 +53882,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -53926,7 +53926,7 @@
         <v>45343</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -53983,7 +53983,7 @@
         <v>45345</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54040,7 +54040,7 @@
         <v>45345</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -569,7 +569,7 @@
         <v>45187</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44208</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44742</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>44760</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44923</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44965</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44977</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44977</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45070</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45077</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43318</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>43322</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>43340</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>43340</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>43340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>43355</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>43355</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>43362</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>43368</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43376</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43377</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43383</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>43383</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>43384</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>43385</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>43391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>43402</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>43411</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>43411</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>43412</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>43416</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>43418</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>43418</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>43418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>43419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>43419</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>43419</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>43420</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>43423</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>43423</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43429</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43430</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43430</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43431</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43437</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43438</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43440</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43440</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43446</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43446</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43461</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43461</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43467</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43487</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43490</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43493</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43493</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43493</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>43494</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>43495</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>43495</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>43495</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>43495</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>43499</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43501</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>43503</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>43503</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43503</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>43504</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>43504</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>43504</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>43504</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>43509</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>43509</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>43510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>43516</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>43516</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>43516</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>43517</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>43524</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>43529</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>43529</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>43529</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>43530</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>43530</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>43535</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>43539</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>43541</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>43543</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>43543</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>43545</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>43551</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>43556</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43557</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43557</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43558</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43558</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43563</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>43566</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>43567</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>43567</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>43579</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>43579</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>43584</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43587</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43587</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>43599</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>43600</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43602</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43605</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43605</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>43607</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>43612</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43612</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>43619</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>43623</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>43634</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>43643</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>43648</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43650</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43650</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43650</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43650</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43650</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43654</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43656</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43657</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43663</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43664</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43678</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43689</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43690</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43691</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>43691</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43692</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>43692</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>43696</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>43697</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>43697</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>43704</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>43704</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>43710</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>43713</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>43713</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>43717</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>43720</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>43725</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43727</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>43727</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>43727</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>43742</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>43760</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43771</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43771</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43775</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43782</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43787</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43791</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>43791</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>43791</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>43791</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>43797</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>43797</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>43804</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>43805</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>43810</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>43810</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>43810</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>43810</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>43811</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>43815</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>43838</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>43838</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>43838</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>43838</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43841</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>43847</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>43858</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>43865</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>43868</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>43871</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>43882</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>43885</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>43886</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>43886</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>43889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>43889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43893</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>43893</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>43899</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>43901</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>43902</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>43902</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43903</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43908</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>43909</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>43909</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>43910</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>43922</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>43923</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>43937</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>43937</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43937</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43937</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43943</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43943</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43948</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43949</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43955</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43966</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43969</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43974</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43975</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43989</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43998</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44000</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44004</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44004</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44004</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44014</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44015</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44022</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44022</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44022</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44022</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44022</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44022</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44025</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44027</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44039</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44047</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44055</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44064</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44064</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44066</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44066</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44066</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44069</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44070</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44078</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44081</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44083</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44083</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44083</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44088</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44090</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>44099</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44100</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44103</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>44111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44118</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44119</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44126</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44133</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44133</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44138</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44138</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44145</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44146</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44159</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>44159</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44161</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44161</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44165</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>44165</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44166</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>44173</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44209</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44215</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44216</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44224</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44228</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44228</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44232</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44235</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>44236</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>44236</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44237</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44237</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44239</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44242</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44243</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44243</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44245</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>44250</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44250</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44250</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44265</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44266</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44271</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44272</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44273</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44273</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44273</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44273</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44275</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44278</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44284</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44284</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44285</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44287</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44293</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44297</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44299</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44302</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44302</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44305</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44308</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44316</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44319</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44322</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44323</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44328</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44333</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44337</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44340</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44343</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44344</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44353</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44353</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44353</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44353</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44354</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44355</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44356</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44358</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44358</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44358</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>44358</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44358</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44358</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44362</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44365</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44365</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44365</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44376</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44378</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44378</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44378</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>44378</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44378</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44379</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44386</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44386</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44389</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44389</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44392</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44396</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44397</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44400</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44406</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44406</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44414</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44414</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44414</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44414</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44417</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44425</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44428</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44432</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44432</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44433</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44435</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44441</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44447</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44449</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44454</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44455</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44455</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44455</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44455</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44456</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>44456</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>44456</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44459</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44462</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>44463</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44465</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>44467</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44467</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44469</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44469</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44473</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44473</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44474</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44488</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44488</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44489</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44489</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44489</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44495</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44495</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44496</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44496</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44497</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44498</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44502</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44507</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44508</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44516</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44522</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44523</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44523</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44523</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44529</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44530</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44544</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44544</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44547</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44550</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44551</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44551</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44551</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44551</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44551</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44553</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44558</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44558</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44558</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44563</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44563</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44571</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44575</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44575</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44578</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44578</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44585</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>44594</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44594</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44606</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44606</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44606</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44606</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44607</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44607</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44614</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44614</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44615</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44621</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44626</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44638</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44648</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44651</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44657</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44662</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44662</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44694</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44694</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44697</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44699</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44700</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44712</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44712</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44712</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>44712</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>44715</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44721</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>44729</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>44732</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44735</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44735</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>44735</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44739</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44739</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44739</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>44739</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>44748</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>44748</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44748</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44748</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44749</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>44749</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44753</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>44753</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44767</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>44771</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>44776</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>44776</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>44791</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44802</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>44802</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44802</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44802</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44802</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44802</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44806</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44806</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44809</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44809</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44810</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44810</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44812</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44812</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44817</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44817</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44818</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44819</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44820</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44824</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44824</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44840</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44840</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44840</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44840</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44840</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>44840</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>44845</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44853</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44853</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>44855</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44860</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44860</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44865</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44866</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44866</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44867</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44867</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44873</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>44873</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>44880</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>44887</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>44888</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44893</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44893</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44894</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44894</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44896</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44896</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44896</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44896</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>44902</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44903</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44903</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44903</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44907</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44908</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>44909</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44910</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44910</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44915</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44923</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44923</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>44923</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>44926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>44931</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>44931</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44931</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>44931</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44931</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44931</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44935</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44938</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44943</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44945</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44949</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44949</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>44950</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44951</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>44952</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44952</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>44958</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>44958</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>44961</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>44966</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>44966</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>44970</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44970</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44971</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>44971</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>44971</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>44972</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>44972</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>44974</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>44974</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44974</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>44974</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>44977</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>44986</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>44986</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44986</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>44986</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>44995</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45000</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>45002</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45008</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45008</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45008</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>45009</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45009</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45009</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45009</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>45012</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45012</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45012</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45012</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45026</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45027</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45027</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45042</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45042</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45042</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45051</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45051</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45054</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45054</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45062</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45075</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45077</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45078</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45084</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45089</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45089</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45089</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45091</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45091</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45092</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45093</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45093</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45093</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45093</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45095</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45096</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45096</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45096</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45097</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45097</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45097</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45097</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45097</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45097</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45098</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>45098</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>45098</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45099</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45100</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45100</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45100</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45100</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45103</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45103</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45103</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45104</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45104</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45105</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45110</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45110</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45110</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45110</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45112</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45112</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45113</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45113</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45113</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45117</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45118</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45118</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45119</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45120</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45125</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45131</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45133</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45135</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45140</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45153</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45154</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45154</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45155</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45155</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45159</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45159</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45159</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45161</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45161</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45163</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45163</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45163</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45163</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45166</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45167</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45167</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45169</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45170</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45174</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45174</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45175</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45175</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45176</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45176</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>45177</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45177</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45180</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45182</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45183</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45187</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45187</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45189</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45189</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>45189</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45190</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45190</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45190</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45191</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45191</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45191</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45191</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>45191</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45191</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45196</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45198</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45198</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45198</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45199</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45201</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45201</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45204</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45204</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45211</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45211</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45211</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45211</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45211</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45211</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45212</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45212</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45212</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45218</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45223</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45229</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45230</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45231</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45231</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45233</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45235</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45235</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45235</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45235</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45235</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45235</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45236</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45237</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45237</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45240</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45244</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45245</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45246</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45247</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45247</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45250</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45250</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45250</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45250</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45250</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45251</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45254</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45257</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45258</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45259</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45260</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45266</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45266</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
         <v>45270</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45271</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45273</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50828,7 +50828,7 @@
         <v>45273</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45273</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45273</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50999,7 +50999,7 @@
         <v>45273</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45274</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>45274</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45282</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45282</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45282</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45301</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>45305</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45308</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45308</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45308</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>45315</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45315</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>45316</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>45316</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -51854,7 +51854,7 @@
         <v>45316</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45316</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45317</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52018,14 +52018,14 @@
     <row r="892" ht="15" customHeight="1">
       <c r="A892" t="inlineStr">
         <is>
-          <t>A 3439-2024</t>
+          <t>A 3556-2024</t>
         </is>
       </c>
       <c r="B892" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         </is>
       </c>
       <c r="G892" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -52075,14 +52075,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 3552-2024</t>
+          <t>A 3583-2024</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -52132,14 +52132,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 3579-2024</t>
+          <t>A 3584-2024</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         </is>
       </c>
       <c r="G894" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -52189,14 +52189,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 3583-2024</t>
+          <t>A 3554-2024</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52246,14 +52246,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 3455-2024</t>
+          <t>A 3582-2024</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -52303,14 +52303,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 3553-2024</t>
+          <t>A 3455-2024</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -52360,14 +52360,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 3581-2024</t>
+          <t>A 3553-2024</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>8.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -52417,14 +52417,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 3585-2024</t>
+          <t>A 3581-2024</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>0.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -52474,14 +52474,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 3554-2024</t>
+          <t>A 3585-2024</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -52531,14 +52531,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 3582-2024</t>
+          <t>A 3552-2024</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -52588,14 +52588,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 3584-2024</t>
+          <t>A 3579-2024</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -52645,14 +52645,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 3556-2024</t>
+          <t>A 3439-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -52709,7 +52709,7 @@
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45322</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52816,14 +52816,14 @@
     <row r="906" ht="15" customHeight="1">
       <c r="A906" t="inlineStr">
         <is>
-          <t>A 4223-2024</t>
+          <t>A 4226-2024</t>
         </is>
       </c>
       <c r="B906" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -52841,7 +52841,7 @@
         </is>
       </c>
       <c r="G906" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="H906" t="n">
         <v>0</v>
@@ -52878,14 +52878,14 @@
     <row r="907" ht="15" customHeight="1">
       <c r="A907" t="inlineStr">
         <is>
-          <t>A 4226-2024</t>
+          <t>A 4223-2024</t>
         </is>
       </c>
       <c r="B907" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         </is>
       </c>
       <c r="G907" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="H907" t="n">
         <v>0</v>
@@ -52947,7 +52947,7 @@
         <v>45328</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45328</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>45329</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53111,14 +53111,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 4990-2024</t>
+          <t>A 4992-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53168,14 +53168,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 4994-2024</t>
+          <t>A 4990-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53225,14 +53225,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 4992-2024</t>
+          <t>A 4994-2024</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         </is>
       </c>
       <c r="G913" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -53289,7 +53289,7 @@
         <v>45331</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45331</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53403,7 +53403,7 @@
         <v>45331</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53460,7 +53460,7 @@
         <v>45331</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53517,7 +53517,7 @@
         <v>45331</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53567,14 +53567,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 6207-2024</t>
+          <t>A 6202-2024</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -53624,14 +53624,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 6201-2024</t>
+          <t>A 6207-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -53681,14 +53681,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 6202-2024</t>
+          <t>A 6201-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -53745,7 +53745,7 @@
         <v>45341</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>45342</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45342</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45343</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -53976,14 +53976,14 @@
     <row r="926" ht="15" customHeight="1">
       <c r="A926" t="inlineStr">
         <is>
-          <t>A 7369-2024</t>
+          <t>A 7367-2024</t>
         </is>
       </c>
       <c r="B926" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54033,14 +54033,14 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>A 7367-2024</t>
+          <t>A 7369-2024</t>
         </is>
       </c>
       <c r="B927" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z927"/>
+  <dimension ref="A1:Z928"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45187</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44208</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44742</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>44760</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44923</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44965</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44977</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44977</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45070</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45077</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43318</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>43322</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>43340</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>43340</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>43340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>43355</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>43355</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>43362</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>43368</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43376</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43377</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43383</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>43383</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>43384</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>43385</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>43391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>43402</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>43411</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>43411</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>43412</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>43416</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>43418</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>43418</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>43418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>43419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>43419</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>43419</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>43420</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>43423</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>43423</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43429</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43430</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43430</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43431</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43437</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43438</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43440</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43440</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43446</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43446</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43461</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43461</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43467</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43487</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43490</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43493</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43493</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43493</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>43494</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>43495</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>43495</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>43495</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>43495</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>43499</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43501</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>43503</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>43503</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43503</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>43504</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>43504</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>43504</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>43504</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>43509</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>43509</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>43510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>43516</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>43516</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>43516</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>43517</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>43524</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>43529</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>43529</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>43529</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>43530</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>43530</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>43535</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>43539</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>43541</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>43543</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>43543</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>43545</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>43551</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>43556</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43557</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43557</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43558</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43558</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43563</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>43566</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>43567</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>43567</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>43579</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>43579</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>43584</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43587</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43587</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>43599</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>43600</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43602</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43605</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43605</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>43607</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>43612</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43612</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>43619</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>43623</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>43634</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>43643</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>43648</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43650</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43650</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43650</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43650</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43650</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43654</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43656</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43657</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43663</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43664</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43678</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43689</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43690</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43691</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>43691</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43692</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>43692</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>43696</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>43697</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>43697</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>43704</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>43704</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>43710</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>43713</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>43713</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>43717</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>43720</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>43725</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43727</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>43727</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>43727</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>43742</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>43760</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43771</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43771</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43775</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43782</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43787</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43791</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>43791</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>43791</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>43791</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>43797</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>43797</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>43804</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>43805</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>43810</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>43810</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>43810</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>43810</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>43811</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>43815</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>43838</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>43838</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>43838</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>43838</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43841</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>43847</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>43858</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>43865</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>43868</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>43871</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>43882</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>43885</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>43886</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>43886</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>43889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>43889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43893</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>43893</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>43899</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>43901</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>43902</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>43902</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43903</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43908</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>43909</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>43909</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>43910</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>43922</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>43923</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>43937</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>43937</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43937</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43937</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43943</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43943</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43948</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43949</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43955</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43966</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43969</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43974</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43975</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43989</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43998</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44000</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44004</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44004</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44004</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44014</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44015</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44022</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44022</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44022</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44022</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44022</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44022</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44025</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44027</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44039</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44047</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44055</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44064</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44064</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44066</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44066</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44066</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44069</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44070</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44078</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44081</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44083</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44083</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44083</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44088</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44090</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>44099</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44100</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44103</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>44111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44118</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44119</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44126</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44133</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44133</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44138</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44138</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44145</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44146</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44159</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>44159</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44161</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44161</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44165</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>44165</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44166</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>44173</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44209</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44215</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44216</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44224</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44228</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44228</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44232</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44235</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>44236</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>44236</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44237</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44237</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44239</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44242</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44243</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44243</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44245</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>44250</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44250</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44250</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44265</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44266</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44271</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44272</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44273</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44273</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44273</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44273</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44275</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44278</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44284</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44284</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44285</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44287</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44293</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44297</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44299</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44302</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44302</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44305</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44308</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44316</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44319</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44322</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44323</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44328</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44333</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44337</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44340</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44343</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44344</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44353</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44353</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44353</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44353</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44354</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44355</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44356</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44358</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44358</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44358</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>44358</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44358</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44358</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44362</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44365</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44365</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44365</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44376</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44378</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44378</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44378</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>44378</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44378</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44379</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44386</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44386</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44389</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44389</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44392</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44396</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44397</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44400</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44406</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44406</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44414</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44414</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44414</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44414</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44417</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44425</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44428</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44432</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44432</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44433</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44435</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44441</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44447</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44449</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44454</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44455</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44455</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44455</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44455</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44456</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>44456</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>44456</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44459</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44462</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>44463</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44465</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>44467</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44467</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44469</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44469</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44473</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44473</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44474</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44488</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44488</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44489</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44489</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44489</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44495</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44495</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44496</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44496</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44497</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44498</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44502</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44507</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44508</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44516</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44522</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44523</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44523</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44523</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44529</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44530</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44544</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44544</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44547</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44550</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44551</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44551</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44551</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44551</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44551</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44553</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44558</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44558</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44558</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44563</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44563</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44571</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44575</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44575</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44578</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44578</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44585</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>44594</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44594</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44606</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44606</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44606</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44606</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44607</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44607</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44614</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44614</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44615</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44621</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44626</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44638</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44648</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44651</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44657</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44662</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44662</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44694</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44694</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44697</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44699</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44700</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44712</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44712</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44712</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>44712</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>44715</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44721</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>44729</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>44732</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44735</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44735</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>44735</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44739</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44739</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44739</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>44739</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>44748</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>44748</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44748</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44748</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44749</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>44749</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44753</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>44753</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44767</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>44771</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>44776</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>44776</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>44791</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44802</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>44802</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44802</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44802</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44802</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44802</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44806</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44806</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44809</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44809</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44810</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44810</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44812</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44812</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44817</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44817</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44818</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44819</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44820</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44824</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44824</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44840</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44840</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44840</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44840</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44840</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>44840</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>44845</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44853</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44853</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>44855</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44860</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44860</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44865</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44866</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44866</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44867</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44867</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44873</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>44873</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>44880</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>44887</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>44888</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44893</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44893</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44894</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44894</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44896</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44896</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44896</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44896</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>44902</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44903</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44903</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44903</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44907</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44908</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>44909</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44910</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44910</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44915</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44923</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44923</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>44923</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>44926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>44931</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>44931</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44931</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>44931</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44931</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44931</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44935</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44938</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44943</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44945</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44949</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44949</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>44950</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44951</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>44952</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44952</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>44958</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>44958</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>44961</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>44966</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>44966</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>44970</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44970</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44971</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>44971</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>44971</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>44972</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>44972</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>44974</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>44974</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44974</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>44974</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>44977</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>44986</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>44986</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44986</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>44986</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>44995</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45000</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>45002</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45008</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45008</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45008</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>45009</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45009</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45009</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45009</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>45012</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45012</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45012</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45012</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45026</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45027</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45027</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45042</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45042</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45042</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45051</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45051</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45054</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45054</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45062</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45075</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45077</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45078</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45084</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45089</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45089</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45089</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45091</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45091</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45092</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45093</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45093</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45093</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45093</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45095</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45096</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45096</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45096</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45097</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45097</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45097</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45097</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45097</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45097</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45098</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>45098</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>45098</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45099</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45100</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45100</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45100</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45100</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45103</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45103</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45103</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45104</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45104</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45105</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45110</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45110</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45110</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45110</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45112</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45112</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45113</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45113</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45113</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45117</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45118</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45118</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45119</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45120</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45125</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45131</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45133</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45135</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45140</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45153</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45154</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45154</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45155</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45155</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45159</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45159</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45159</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45161</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45161</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45163</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45163</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45163</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45163</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45166</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45167</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45167</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45169</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45170</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45174</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45174</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45175</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45175</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45176</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45176</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>45177</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45177</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45180</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45182</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45183</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45187</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45187</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45189</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45189</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>45189</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45190</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45190</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45190</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45191</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45191</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45191</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45191</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>45191</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45191</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45196</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45198</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45198</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45198</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45199</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45201</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45201</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45204</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45204</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45211</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45211</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45211</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45211</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45211</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45211</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45212</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45212</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45212</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45218</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45223</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45229</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45230</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45231</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45231</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45233</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45235</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45235</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45235</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45235</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45235</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45235</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45236</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45237</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45237</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45240</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45244</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45245</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45246</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45247</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45247</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45250</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45250</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45250</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45250</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45250</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45251</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45254</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45257</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45258</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45259</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45260</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45266</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45266</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
         <v>45270</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45271</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45273</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50828,7 +50828,7 @@
         <v>45273</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45273</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45273</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50999,7 +50999,7 @@
         <v>45273</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45274</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>45274</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45282</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45282</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45282</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45301</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>45305</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45308</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45308</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45308</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>45315</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45315</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>45316</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>45316</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -51854,7 +51854,7 @@
         <v>45316</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45316</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45317</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52018,14 +52018,14 @@
     <row r="892" ht="15" customHeight="1">
       <c r="A892" t="inlineStr">
         <is>
-          <t>A 3556-2024</t>
+          <t>A 3455-2024</t>
         </is>
       </c>
       <c r="B892" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         </is>
       </c>
       <c r="G892" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -52075,14 +52075,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 3583-2024</t>
+          <t>A 3553-2024</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -52132,14 +52132,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 3584-2024</t>
+          <t>A 3581-2024</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         </is>
       </c>
       <c r="G894" t="n">
-        <v>1.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -52189,14 +52189,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 3554-2024</t>
+          <t>A 3439-2024</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52246,14 +52246,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 3582-2024</t>
+          <t>A 3552-2024</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -52303,14 +52303,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 3455-2024</t>
+          <t>A 3556-2024</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -52360,14 +52360,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 3553-2024</t>
+          <t>A 3584-2024</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -52417,14 +52417,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 3581-2024</t>
+          <t>A 3554-2024</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -52481,7 +52481,7 @@
         <v>45320</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52531,14 +52531,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 3552-2024</t>
+          <t>A 3582-2024</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         </is>
       </c>
       <c r="G901" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -52595,7 +52595,7 @@
         <v>45320</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52645,14 +52645,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 3439-2024</t>
+          <t>A 3583-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         </is>
       </c>
       <c r="G903" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="H903" t="n">
         <v>0</v>
@@ -52702,14 +52702,14 @@
     <row r="904" ht="15" customHeight="1">
       <c r="A904" t="inlineStr">
         <is>
-          <t>A 3975-2024</t>
+          <t>A 3899-2024</t>
         </is>
       </c>
       <c r="B904" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         </is>
       </c>
       <c r="G904" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -52759,14 +52759,14 @@
     <row r="905" ht="15" customHeight="1">
       <c r="A905" t="inlineStr">
         <is>
-          <t>A 3899-2024</t>
+          <t>A 3975-2024</t>
         </is>
       </c>
       <c r="B905" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         </is>
       </c>
       <c r="G905" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -52823,7 +52823,7 @@
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -52885,7 +52885,7 @@
         <v>45324</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -52947,7 +52947,7 @@
         <v>45328</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45328</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53054,14 +53054,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 4991-2024</t>
+          <t>A 4990-2024</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53111,14 +53111,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 4992-2024</t>
+          <t>A 4994-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53168,14 +53168,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 4990-2024</t>
+          <t>A 4992-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53225,14 +53225,14 @@
     <row r="913" ht="15" customHeight="1">
       <c r="A913" t="inlineStr">
         <is>
-          <t>A 4994-2024</t>
+          <t>A 4991-2024</t>
         </is>
       </c>
       <c r="B913" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         </is>
       </c>
       <c r="G913" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H913" t="n">
         <v>0</v>
@@ -53282,14 +53282,14 @@
     <row r="914" ht="15" customHeight="1">
       <c r="A914" t="inlineStr">
         <is>
-          <t>A 5337-2024</t>
+          <t>A 5334-2024</t>
         </is>
       </c>
       <c r="B914" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         </is>
       </c>
       <c r="G914" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="H914" t="n">
         <v>0</v>
@@ -53339,14 +53339,14 @@
     <row r="915" ht="15" customHeight="1">
       <c r="A915" t="inlineStr">
         <is>
-          <t>A 5334-2024</t>
+          <t>A 5335-2024</t>
         </is>
       </c>
       <c r="B915" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         </is>
       </c>
       <c r="G915" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -53396,14 +53396,14 @@
     <row r="916" ht="15" customHeight="1">
       <c r="A916" t="inlineStr">
         <is>
-          <t>A 5335-2024</t>
+          <t>A 5282-2024</t>
         </is>
       </c>
       <c r="B916" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         </is>
       </c>
       <c r="G916" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -53453,14 +53453,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 5282-2024</t>
+          <t>A 5336-2024</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>6.6</v>
+        <v>0.3</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53510,14 +53510,14 @@
     <row r="918" ht="15" customHeight="1">
       <c r="A918" t="inlineStr">
         <is>
-          <t>A 5336-2024</t>
+          <t>A 5337-2024</t>
         </is>
       </c>
       <c r="B918" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         </is>
       </c>
       <c r="G918" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -53574,7 +53574,7 @@
         <v>45337</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53624,14 +53624,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 6207-2024</t>
+          <t>A 6201-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -53681,14 +53681,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 6201-2024</t>
+          <t>A 6207-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -53745,7 +53745,7 @@
         <v>45341</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -53795,14 +53795,14 @@
     <row r="923" ht="15" customHeight="1">
       <c r="A923" t="inlineStr">
         <is>
-          <t>A 6776-2024</t>
+          <t>A 6774-2024</t>
         </is>
       </c>
       <c r="B923" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         </is>
       </c>
       <c r="G923" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -53857,14 +53857,14 @@
     <row r="924" ht="15" customHeight="1">
       <c r="A924" t="inlineStr">
         <is>
-          <t>A 6774-2024</t>
+          <t>A 6776-2024</t>
         </is>
       </c>
       <c r="B924" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -53882,7 +53882,7 @@
         </is>
       </c>
       <c r="G924" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="H924" t="n">
         <v>0</v>
@@ -53926,7 +53926,7 @@
         <v>45343</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -53983,7 +53983,7 @@
         <v>45345</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
       </c>
       <c r="R926" s="2" t="inlineStr"/>
     </row>
-    <row r="927">
+    <row r="927" ht="15" customHeight="1">
       <c r="A927" t="inlineStr">
         <is>
           <t>A 7369-2024</t>
@@ -54040,7 +54040,7 @@
         <v>45345</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54086,6 +54086,63 @@
         <v>0</v>
       </c>
       <c r="R927" s="2" t="inlineStr"/>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>A 7648-2024</t>
+        </is>
+      </c>
+      <c r="B928" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C928" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>GISLAVED</t>
+        </is>
+      </c>
+      <c r="G928" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H928" t="n">
+        <v>0</v>
+      </c>
+      <c r="I928" t="n">
+        <v>0</v>
+      </c>
+      <c r="J928" t="n">
+        <v>0</v>
+      </c>
+      <c r="K928" t="n">
+        <v>0</v>
+      </c>
+      <c r="L928" t="n">
+        <v>0</v>
+      </c>
+      <c r="M928" t="n">
+        <v>0</v>
+      </c>
+      <c r="N928" t="n">
+        <v>0</v>
+      </c>
+      <c r="O928" t="n">
+        <v>0</v>
+      </c>
+      <c r="P928" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q928" t="n">
+        <v>0</v>
+      </c>
+      <c r="R928" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z928"/>
+  <dimension ref="A1:Z930"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45187</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44208</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44742</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>44760</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44923</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44965</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44977</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44977</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45070</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45077</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43318</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>43322</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>43340</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>43340</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>43340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>43355</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>43355</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>43362</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>43368</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43376</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43377</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43383</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>43383</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>43384</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>43385</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>43391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>43402</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>43411</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>43411</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>43412</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>43416</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>43418</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>43418</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>43418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>43419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>43419</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>43419</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>43420</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>43423</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>43423</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43429</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43430</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43430</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43431</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43437</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43438</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43440</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43440</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43446</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43446</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43461</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43461</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43467</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43487</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43490</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43493</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43493</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43493</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>43494</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>43495</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>43495</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>43495</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>43495</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>43499</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43501</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>43503</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>43503</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43503</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>43504</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>43504</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>43504</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>43504</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>43509</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>43509</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>43510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>43516</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>43516</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>43516</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>43517</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>43524</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>43529</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>43529</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>43529</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>43530</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>43530</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>43535</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>43539</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>43541</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>43543</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>43543</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>43545</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>43551</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>43556</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43557</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43557</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43558</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43558</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43563</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>43566</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>43567</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>43567</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>43579</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>43579</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>43584</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43587</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43587</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>43599</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>43600</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43602</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43605</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43605</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>43607</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>43612</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43612</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>43619</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>43623</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>43634</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>43643</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>43648</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43650</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43650</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43650</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43650</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43650</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43654</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43656</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43657</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43663</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43664</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43678</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43689</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43690</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43691</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>43691</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43692</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>43692</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>43696</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>43697</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>43697</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>43704</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>43704</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>43710</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>43713</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>43713</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>43717</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>43720</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>43725</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43727</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>43727</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>43727</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>43742</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>43760</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43771</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43771</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43775</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43782</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43787</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43791</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>43791</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>43791</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>43791</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>43797</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>43797</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>43804</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>43805</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>43810</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>43810</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>43810</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>43810</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>43811</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>43815</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>43838</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>43838</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>43838</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>43838</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43841</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>43847</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>43858</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>43865</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>43868</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>43871</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>43882</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>43885</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>43886</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>43886</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>43889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>43889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43893</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>43893</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>43899</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>43901</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>43902</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>43902</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43903</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43908</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>43909</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>43909</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>43910</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>43922</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>43923</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>43937</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>43937</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43937</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43937</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43943</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43943</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43948</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43949</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43955</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43966</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43969</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43974</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43975</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43989</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43998</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44000</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44004</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44004</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44004</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44014</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44015</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44022</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44022</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44022</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44022</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44022</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44022</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44025</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44027</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44039</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44047</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44055</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44064</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44064</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44066</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44066</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44066</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44069</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44070</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44078</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44081</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44083</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44083</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44083</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44088</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44090</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>44099</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44100</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44103</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>44111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44118</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44119</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44126</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44133</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44133</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44138</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44138</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44145</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44146</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44159</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>44159</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44161</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44161</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44165</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>44165</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44166</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>44173</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44209</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44215</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44216</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44224</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44228</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44228</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44232</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44235</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>44236</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>44236</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44237</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44237</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44239</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44242</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44243</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44243</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44245</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>44250</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44250</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44250</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44265</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44266</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44271</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44272</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44273</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44273</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44273</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44273</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44275</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44278</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44284</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44284</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44285</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44287</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44293</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44297</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44299</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44302</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44302</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44305</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44308</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44316</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44319</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44322</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44323</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44328</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44333</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44337</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44340</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44343</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44344</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44353</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44353</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44353</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44353</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44354</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44355</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44356</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44358</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44358</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44358</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>44358</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44358</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44358</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44362</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44365</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44365</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44365</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44376</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44378</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44378</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44378</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>44378</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44378</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44379</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44386</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44386</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44389</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44389</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44392</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44396</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44397</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44400</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44406</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44406</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44414</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44414</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44414</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44414</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44417</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44425</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44428</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44432</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44432</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44433</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44435</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44441</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44447</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44449</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44454</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44455</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44455</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44455</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44455</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44456</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>44456</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>44456</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44459</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44462</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>44463</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44465</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>44467</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44467</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44469</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44469</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44473</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44473</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44474</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44488</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44488</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44489</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44489</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44489</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44495</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44495</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44496</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44496</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44497</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44498</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44502</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44507</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44508</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44516</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44522</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44523</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44523</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44523</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44529</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44530</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44544</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44544</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44547</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44550</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44551</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44551</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44551</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44551</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44551</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44553</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44558</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44558</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44558</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44563</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44563</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44571</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44575</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44575</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44578</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44578</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44585</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>44594</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44594</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44606</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44606</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44606</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44606</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44607</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44607</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44614</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44614</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44615</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44621</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44626</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44638</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44648</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44651</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44657</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44662</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44662</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44694</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44694</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44697</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44699</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44700</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44712</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44712</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44712</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>44712</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>44715</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44721</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>44729</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>44732</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44735</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44735</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>44735</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44739</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44739</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44739</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>44739</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>44748</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>44748</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44748</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44748</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44749</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>44749</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44753</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>44753</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44767</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>44771</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>44776</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>44776</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>44791</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44802</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>44802</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44802</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44802</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44802</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44802</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44806</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44806</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44809</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44809</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44810</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44810</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44812</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44812</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44817</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44817</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44818</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44819</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44820</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44824</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44824</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44840</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44840</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>44840</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44840</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44840</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>44840</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>44845</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44853</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44853</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>44855</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>44860</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44860</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44865</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44866</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44866</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44866</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44866</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44867</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44867</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44873</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35328,7 +35328,7 @@
         <v>44873</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         <v>44880</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>44887</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>44888</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>44893</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>44893</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>44894</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44894</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44896</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44896</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>44896</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44896</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>44902</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44903</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44903</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44903</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44903</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44907</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44908</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44909</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>44909</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44910</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>44910</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>44915</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36701,7 +36701,7 @@
         <v>44917</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44923</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44923</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>44923</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>44923</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -36991,7 +36991,7 @@
         <v>44926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>44926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>44931</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>44931</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44931</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>44931</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44931</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44931</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44935</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44938</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44943</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44945</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44949</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44949</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37794,7 +37794,7 @@
         <v>44950</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>44951</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>44952</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>44952</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>44958</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>44958</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38136,7 +38136,7 @@
         <v>44961</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>44966</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>44966</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>44970</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44970</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44971</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>44971</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>44971</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>44972</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>44972</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>44974</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>44974</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>44974</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>44974</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>44977</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>44986</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>44986</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>44986</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>44986</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>44995</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45000</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>45002</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45008</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45008</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45008</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>45009</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45009</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45009</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45009</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39789,7 +39789,7 @@
         <v>45012</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39846,7 +39846,7 @@
         <v>45012</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>45012</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45012</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45026</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45027</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45027</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45042</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45042</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45042</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>45051</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45051</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45054</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45054</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45062</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45075</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45077</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45078</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45084</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45084</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45086</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45089</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45089</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45089</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45091</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45091</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45092</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45093</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45093</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45093</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45093</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45095</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45096</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45096</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45096</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45097</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45097</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45097</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45097</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45097</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45097</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45098</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>45098</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>45098</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45099</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45100</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42456,7 +42456,7 @@
         <v>45100</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45100</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45100</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45103</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45103</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45103</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45104</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45104</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45105</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45106</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>45110</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45110</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45110</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>45110</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>45111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45112</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45112</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45113</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45113</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45113</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45117</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45118</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45118</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45119</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45120</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45125</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45131</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45133</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45135</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45140</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45153</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45154</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45154</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45155</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45155</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45155</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45159</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45159</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45159</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45161</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45161</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45163</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45163</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45163</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45163</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45166</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45167</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45167</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45169</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45170</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45174</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45174</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45175</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45175</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45176</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45176</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>45177</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45177</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45180</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45182</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45183</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45187</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45187</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45189</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45189</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>45189</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45190</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>45190</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45190</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45191</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>45191</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>45191</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45191</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -46647,7 +46647,7 @@
         <v>45191</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45191</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45196</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45196</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45196</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45198</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45198</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45198</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>45198</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47180,7 +47180,7 @@
         <v>45199</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45201</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         <v>45201</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45204</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45204</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45211</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45211</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45211</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45211</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45211</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45211</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45212</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45212</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45212</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45218</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45223</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45223</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45223</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45229</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45230</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45231</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45231</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45233</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45235</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45235</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45235</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45235</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45235</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45235</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45236</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45237</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45237</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45237</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45240</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45244</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45245</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45246</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45247</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45247</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45250</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>45250</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45250</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45250</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45250</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45251</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45254</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45257</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45258</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45259</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45260</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>45264</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45264</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45264</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>45264</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45264</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45264</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45264</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50543,7 +50543,7 @@
         <v>45266</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45266</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
         <v>45270</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>45271</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45273</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -50828,7 +50828,7 @@
         <v>45273</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45273</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45273</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -50999,7 +50999,7 @@
         <v>45273</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45274</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>45274</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>45282</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45282</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45282</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45301</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         <v>45305</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51455,7 +51455,7 @@
         <v>45308</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45308</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45308</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>45315</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45315</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>45316</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -51797,7 +51797,7 @@
         <v>45316</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -51854,7 +51854,7 @@
         <v>45316</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45316</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45317</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45320</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52075,14 +52075,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 3553-2024</t>
+          <t>A 3439-2024</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -52132,14 +52132,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 3581-2024</t>
+          <t>A 3552-2024</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         </is>
       </c>
       <c r="G894" t="n">
-        <v>8.800000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -52189,14 +52189,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 3439-2024</t>
+          <t>A 3553-2024</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52246,14 +52246,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 3552-2024</t>
+          <t>A 3556-2024</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -52303,14 +52303,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 3556-2024</t>
+          <t>A 3584-2024</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -52360,14 +52360,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 3584-2024</t>
+          <t>A 3581-2024</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>1.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -52424,7 +52424,7 @@
         <v>45320</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52474,14 +52474,14 @@
     <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
-          <t>A 3585-2024</t>
+          <t>A 3579-2024</t>
         </is>
       </c>
       <c r="B900" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="G900" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -52531,14 +52531,14 @@
     <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
-          <t>A 3582-2024</t>
+          <t>A 3583-2024</t>
         </is>
       </c>
       <c r="B901" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52588,14 +52588,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 3579-2024</t>
+          <t>A 3585-2024</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -52645,14 +52645,14 @@
     <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 3583-2024</t>
+          <t>A 3582-2024</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>45322</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45322</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -52823,7 +52823,7 @@
         <v>45324</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -52885,7 +52885,7 @@
         <v>45324</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -52947,7 +52947,7 @@
         <v>45328</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45328</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53054,14 +53054,14 @@
     <row r="910" ht="15" customHeight="1">
       <c r="A910" t="inlineStr">
         <is>
-          <t>A 4990-2024</t>
+          <t>A 4992-2024</t>
         </is>
       </c>
       <c r="B910" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         </is>
       </c>
       <c r="G910" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="H910" t="n">
         <v>0</v>
@@ -53111,14 +53111,14 @@
     <row r="911" ht="15" customHeight="1">
       <c r="A911" t="inlineStr">
         <is>
-          <t>A 4994-2024</t>
+          <t>A 4990-2024</t>
         </is>
       </c>
       <c r="B911" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         </is>
       </c>
       <c r="G911" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -53168,14 +53168,14 @@
     <row r="912" ht="15" customHeight="1">
       <c r="A912" t="inlineStr">
         <is>
-          <t>A 4992-2024</t>
+          <t>A 4994-2024</t>
         </is>
       </c>
       <c r="B912" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         </is>
       </c>
       <c r="G912" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H912" t="n">
         <v>0</v>
@@ -53232,7 +53232,7 @@
         <v>45329</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53289,7 +53289,7 @@
         <v>45331</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45331</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53403,7 +53403,7 @@
         <v>45331</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53453,14 +53453,14 @@
     <row r="917" ht="15" customHeight="1">
       <c r="A917" t="inlineStr">
         <is>
-          <t>A 5336-2024</t>
+          <t>A 5337-2024</t>
         </is>
       </c>
       <c r="B917" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         </is>
       </c>
       <c r="G917" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -53510,14 +53510,14 @@
     <row r="918" ht="15" customHeight="1">
       <c r="A918" t="inlineStr">
         <is>
-          <t>A 5337-2024</t>
+          <t>A 5336-2024</t>
         </is>
       </c>
       <c r="B918" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         </is>
       </c>
       <c r="G918" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -53567,14 +53567,14 @@
     <row r="919" ht="15" customHeight="1">
       <c r="A919" t="inlineStr">
         <is>
-          <t>A 6202-2024</t>
+          <t>A 6207-2024</t>
         </is>
       </c>
       <c r="B919" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         </is>
       </c>
       <c r="G919" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -53624,14 +53624,14 @@
     <row r="920" ht="15" customHeight="1">
       <c r="A920" t="inlineStr">
         <is>
-          <t>A 6201-2024</t>
+          <t>A 6202-2024</t>
         </is>
       </c>
       <c r="B920" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -53644,7 +53644,7 @@
         </is>
       </c>
       <c r="G920" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="H920" t="n">
         <v>0</v>
@@ -53681,14 +53681,14 @@
     <row r="921" ht="15" customHeight="1">
       <c r="A921" t="inlineStr">
         <is>
-          <t>A 6207-2024</t>
+          <t>A 6201-2024</t>
         </is>
       </c>
       <c r="B921" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         </is>
       </c>
       <c r="G921" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="H921" t="n">
         <v>0</v>
@@ -53745,7 +53745,7 @@
         <v>45341</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>45342</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45342</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45343</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -53983,7 +53983,7 @@
         <v>45345</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54040,7 +54040,7 @@
         <v>45345</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54087,7 +54087,7 @@
       </c>
       <c r="R927" s="2" t="inlineStr"/>
     </row>
-    <row r="928">
+    <row r="928" ht="15" customHeight="1">
       <c r="A928" t="inlineStr">
         <is>
           <t>A 7648-2024</t>
@@ -54097,7 +54097,7 @@
         <v>45348</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54143,6 +54143,120 @@
         <v>0</v>
       </c>
       <c r="R928" s="2" t="inlineStr"/>
+    </row>
+    <row r="929" ht="15" customHeight="1">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>A 7697-2024</t>
+        </is>
+      </c>
+      <c r="B929" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C929" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>GISLAVED</t>
+        </is>
+      </c>
+      <c r="G929" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H929" t="n">
+        <v>0</v>
+      </c>
+      <c r="I929" t="n">
+        <v>0</v>
+      </c>
+      <c r="J929" t="n">
+        <v>0</v>
+      </c>
+      <c r="K929" t="n">
+        <v>0</v>
+      </c>
+      <c r="L929" t="n">
+        <v>0</v>
+      </c>
+      <c r="M929" t="n">
+        <v>0</v>
+      </c>
+      <c r="N929" t="n">
+        <v>0</v>
+      </c>
+      <c r="O929" t="n">
+        <v>0</v>
+      </c>
+      <c r="P929" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q929" t="n">
+        <v>0</v>
+      </c>
+      <c r="R929" s="2" t="inlineStr"/>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>A 7838-2024</t>
+        </is>
+      </c>
+      <c r="B930" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C930" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>JÖNKÖPINGS LÄN</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>GISLAVED</t>
+        </is>
+      </c>
+      <c r="G930" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H930" t="n">
+        <v>0</v>
+      </c>
+      <c r="I930" t="n">
+        <v>0</v>
+      </c>
+      <c r="J930" t="n">
+        <v>0</v>
+      </c>
+      <c r="K930" t="n">
+        <v>0</v>
+      </c>
+      <c r="L930" t="n">
+        <v>0</v>
+      </c>
+      <c r="M930" t="n">
+        <v>0</v>
+      </c>
+      <c r="N930" t="n">
+        <v>0</v>
+      </c>
+      <c r="O930" t="n">
+        <v>0</v>
+      </c>
+      <c r="P930" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q930" t="n">
+        <v>0</v>
+      </c>
+      <c r="R930" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GISLAVED.xlsx
+++ b/Översikt GISLAVED.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z930"/>
+  <dimension ref="A1:Z933"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45187</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44208</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>44530</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44742</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>44760</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44923</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44965</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44977</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44977</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>45070</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45077</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>43318</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>43322</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>43340</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>43340</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>43340</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>43355</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>43355</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>43362</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>43368</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>43376</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>43376</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>43377</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>43383</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>43383</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>43384</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>43385</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>43391</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>43402</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>43411</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>43411</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>43412</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>43416</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>43418</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>43418</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>43418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>43419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>43419</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>43419</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>43420</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>43423</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>43423</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>43429</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>43430</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>43430</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>43431</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>43433</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>43437</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>43438</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>43438</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>43440</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>43440</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>43440</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>43446</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>43446</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>43454</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>43461</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>43461</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>43467</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>43472</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>43473</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>43475</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>43475</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>43487</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>43489</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>43490</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>43493</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>43493</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>43493</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>43493</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>43494</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>43495</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>43495</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>43495</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>43495</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>43499</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43501</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43502</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>43503</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>43503</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43503</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>43504</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>43504</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>43504</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>43504</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>43509</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>43509</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>43510</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>43516</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>43516</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>43516</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>43517</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>43524</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>43529</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>43529</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>43529</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>43530</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>43530</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>43535</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>43539</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>43541</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>43543</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>43543</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>43545</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>43551</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>43556</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>43556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>43557</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>43557</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>43558</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>43558</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>43563</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>43566</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>43567</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>43567</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>43579</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>43579</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>43584</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>43587</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>43587</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>43599</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>43600</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>43602</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>43605</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>43605</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>43607</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>43612</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>43612</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>43619</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>43623</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>43634</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>43643</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>43648</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43650</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43650</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43650</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43650</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43650</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43654</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43656</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43657</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43663</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43664</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43664</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43678</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>43689</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>43690</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>43691</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>43691</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>43692</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>43692</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>43696</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>43697</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>43697</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>43704</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>43704</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>43710</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>43713</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>43713</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>43717</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>43720</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>43725</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43727</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>43727</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>43727</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>43742</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>43760</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>43771</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>43771</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>43775</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>43782</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>43787</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>43791</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>43791</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>43791</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>43791</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>43797</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>43797</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>43804</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>43805</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>43810</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>43810</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>43810</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>43810</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>43811</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>43811</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>43815</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>43838</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>43838</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>43838</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>43838</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>43841</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>43847</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>43858</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>43865</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>43868</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>43871</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>43882</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>43885</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>43886</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>43886</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>43889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>43889</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43893</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>43893</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>43899</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>43901</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>43902</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>43902</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43903</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43908</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>43909</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>43909</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>43910</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         <v>43922</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>43923</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>43937</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>43937</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>43937</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43937</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43943</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43943</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43948</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43949</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43949</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43955</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43966</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43969</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43974</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43975</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43989</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43997</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43998</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44000</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44004</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>44004</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44004</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44014</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>44015</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44022</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44022</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44022</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44022</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>44022</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44022</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>44025</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44027</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44039</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>44047</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44055</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>44063</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44064</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44064</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44066</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44066</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44066</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44069</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>44070</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44078</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44081</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>44083</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>44083</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>44083</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>44088</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44090</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>44099</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44100</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44103</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>44111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44118</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44119</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>44126</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>44133</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44133</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>44138</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44138</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44140</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44145</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44146</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>44148</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44159</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>44159</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44161</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44161</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44165</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>44165</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>44166</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>44173</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>44208</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44208</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44209</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44215</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44216</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44224</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44228</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44228</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44228</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>44232</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44235</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>44236</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>44236</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44236</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44237</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>44237</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>44239</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>44242</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44243</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44243</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44243</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>44244</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>44245</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44246</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>44250</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44250</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44250</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44265</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44265</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44266</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>44266</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44271</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44272</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44273</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44273</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>44273</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44273</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44275</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44278</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44284</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44284</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44285</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44287</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44293</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44297</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44299</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44302</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44302</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44305</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44308</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44316</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44319</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44322</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>44323</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44328</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44333</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44337</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44340</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44343</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>44344</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44353</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44353</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44353</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>44353</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44354</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44355</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>44356</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44358</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44358</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>44358</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>44358</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>44358</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44358</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44362</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44365</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44365</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44365</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44371</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44376</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44378</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44378</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44378</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>44378</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>44378</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44379</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44386</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44386</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44389</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>44389</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44392</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>44396</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>44397</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44400</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44406</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44406</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44414</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44414</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44414</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44414</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44417</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44421</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44421</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44425</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44428</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44432</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44432</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44433</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>44435</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44441</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44441</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44446</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44447</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44447</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44449</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>44454</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44454</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44455</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44455</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44455</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44455</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>44456</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>44456</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>44456</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44459</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44462</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>44463</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44465</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>44467</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44467</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44469</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>44469</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44473</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44473</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>44474</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44482</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44488</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44488</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44489</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44489</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44489</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44495</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44495</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44496</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44496</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>44497</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44498</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44501</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44501</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>44501</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44502</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44507</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44508</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44516</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44522</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44523</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>44523</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44523</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>44529</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>44530</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44544</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27781,7 +27781,7 @@
         <v>44544</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44547</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>44550</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44550</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>44551</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44551</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>44551</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44551</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>44551</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>44553</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44558</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44558</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>44558</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>44563</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44563</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44571</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44575</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44575</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44578</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>44578</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>44578</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44578</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44581</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44585</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44588</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>44588</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44594</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>44594</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44594</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44606</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>44606</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44606</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>44606</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44607</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>44607</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44614</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>44614</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44614</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44614</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44615</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44621</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44624</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44626</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44638</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44648</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44651</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>44657</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44662</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44662</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44691</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44694</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44694</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44697</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44699</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44700</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44711</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44712</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44712</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>44712</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>44712</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>44715</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44721</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>44725</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>44729</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>44732</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44735</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>44735</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>44735</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44739</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44739</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44739</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>44739</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44739</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>44739</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>44748</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>44748</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44748</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44748</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44749</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>44749</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44753</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>44753</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>44757</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44767</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>44771</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32800,7 +32800,7 @@
         <v>44776</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>44776</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>44791</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44802</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>44802</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44802</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44802</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44802</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44802</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44806</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44806</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44809</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44809</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44810</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44810</v>
       </c>